--- a/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6523985228707062</v>
+        <v>0.6657181894367811</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3047970457414124</v>
+        <v>0.3314363788735621</v>
       </c>
       <c r="F2" t="n">
-        <v>1.87685774024499</v>
+        <v>1.991487925457673</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.164</v>
       </c>
       <c r="H2" t="n">
-        <v>223.9380650914103</v>
+        <v>3.434911164195332</v>
       </c>
       <c r="I2" t="n">
-        <v>343.25348271181</v>
+        <v>5.159707543970486</v>
       </c>
       <c r="J2" t="n">
-        <v>14.40243902186523</v>
+        <v>0.3019840033895965</v>
       </c>
       <c r="K2" t="n">
-        <v>5.896581419923804</v>
+        <v>4.996943113347171</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4849451122547849</v>
+        <v>0.4326010350126255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2274176683821775</v>
+        <v>0.1489015525189382</v>
       </c>
       <c r="F3" t="n">
-        <v>1.883081294025797</v>
+        <v>1.524856623671322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.046</v>
+        <v>0.173</v>
       </c>
       <c r="H3" t="n">
-        <v>215.1655066253922</v>
+        <v>3.41981054638972</v>
       </c>
       <c r="I3" t="n">
-        <v>443.6904325624929</v>
+        <v>7.905229691116926</v>
       </c>
       <c r="J3" t="n">
-        <v>9.578757761740095</v>
+        <v>0.1492332621922114</v>
       </c>
       <c r="K3" t="n">
-        <v>5.27600517279251</v>
+        <v>3.402274237945569</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4090966126919534</v>
+        <v>0.2652559831182226</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1980596886533653</v>
+        <v>0.002847405660444946</v>
       </c>
       <c r="F4" t="n">
-        <v>1.938507275708539</v>
+        <v>1.010851038819046</v>
       </c>
       <c r="G4" t="n">
-        <v>0.021</v>
+        <v>0.457</v>
       </c>
       <c r="H4" t="n">
-        <v>226.5356209718211</v>
+        <v>2.733920738517556</v>
       </c>
       <c r="I4" t="n">
-        <v>553.7460197510866</v>
+        <v>10.3067260024784</v>
       </c>
       <c r="J4" t="n">
-        <v>7.426696564075211</v>
+        <v>0.06972885013094039</v>
       </c>
       <c r="K4" t="n">
-        <v>4.897699706710131</v>
+        <v>3.532155939915008</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3156506091888685</v>
+        <v>0.2668195994576067</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1355586642385708</v>
+        <v>0.07387738878855599</v>
       </c>
       <c r="F5" t="n">
-        <v>1.752719197274384</v>
+        <v>1.382899048022602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.018</v>
+        <v>0.157</v>
       </c>
       <c r="H5" t="n">
-        <v>224.3048012451077</v>
+        <v>3.330827788783898</v>
       </c>
       <c r="I5" t="n">
-        <v>710.6110196381584</v>
+        <v>12.48344497763595</v>
       </c>
       <c r="J5" t="n">
-        <v>5.266799119520351</v>
+        <v>0.08710823726539786</v>
       </c>
       <c r="K5" t="n">
-        <v>3.685392051679023</v>
+        <v>4.670193893916771</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2249958990707209</v>
+        <v>0.2505151705239327</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06353671137712102</v>
+        <v>0.09437249771641876</v>
       </c>
       <c r="F6" t="n">
-        <v>1.39351561397481</v>
+        <v>1.604399143549676</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H6" t="n">
-        <v>184.6747577360973</v>
+        <v>3.622972472842313</v>
       </c>
       <c r="I6" t="n">
-        <v>820.7916610873438</v>
+        <v>14.46208812530256</v>
       </c>
       <c r="J6" t="n">
-        <v>2.983657976585868</v>
+        <v>0.08645080993639284</v>
       </c>
       <c r="K6" t="n">
-        <v>4.065910285777069</v>
+        <v>3.599385077299881</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2057824981408733</v>
+        <v>0.2803470166906221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06395794423745771</v>
+        <v>0.151837555385376</v>
       </c>
       <c r="F7" t="n">
-        <v>1.450965241752243</v>
+        <v>2.181528222460752</v>
       </c>
       <c r="G7" t="n">
-        <v>0.078</v>
+        <v>0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>182.2054937428558</v>
+        <v>4.601671985330138</v>
       </c>
       <c r="I7" t="n">
-        <v>885.4275528238688</v>
+        <v>16.41419994280991</v>
       </c>
       <c r="J7" t="n">
-        <v>2.771188240952671</v>
+        <v>0.1027831427396217</v>
       </c>
       <c r="K7" t="n">
-        <v>4.189306871257194</v>
+        <v>3.498906026740482</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1837892223192716</v>
+        <v>0.255569169325842</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06012092267067626</v>
+        <v>0.1427766192236968</v>
       </c>
       <c r="F8" t="n">
-        <v>1.486146594086848</v>
+        <v>2.265833772659613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.073</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>175.0624221570777</v>
+        <v>4.82768773238937</v>
       </c>
       <c r="I8" t="n">
-        <v>952.5173454021478</v>
+        <v>18.88994570481321</v>
       </c>
       <c r="J8" t="n">
-        <v>2.546071413415961</v>
+        <v>0.0887526313465278</v>
       </c>
       <c r="K8" t="n">
-        <v>3.311678717738439</v>
+        <v>2.844188637036549</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1969847115776585</v>
+        <v>0.2346119028123378</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09132480520629771</v>
+        <v>0.1339029426560665</v>
       </c>
       <c r="F9" t="n">
-        <v>1.864327902064577</v>
+        <v>2.329603070553877</v>
       </c>
       <c r="G9" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>215.7257871165769</v>
+        <v>4.852775128084438</v>
       </c>
       <c r="I9" t="n">
-        <v>1095.139746576373</v>
+        <v>20.6842665266054</v>
       </c>
       <c r="J9" t="n">
-        <v>3.13730407055554</v>
+        <v>0.07783701930729836</v>
       </c>
       <c r="K9" t="n">
-        <v>3.29272758456573</v>
+        <v>3.032286700991945</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2031658052182271</v>
+        <v>0.2435437357370023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1083045915537304</v>
+        <v>0.1534894185628358</v>
       </c>
       <c r="F10" t="n">
-        <v>2.141716275492529</v>
+        <v>2.704409331825648</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>249.4608646880759</v>
+        <v>5.552038514240758</v>
       </c>
       <c r="I10" t="n">
-        <v>1227.868363084633</v>
+        <v>22.7968849103813</v>
       </c>
       <c r="J10" t="n">
-        <v>2.86940833390124</v>
+        <v>0.08832746348937695</v>
       </c>
       <c r="K10" t="n">
-        <v>3.324006052145379</v>
+        <v>2.729941736124553</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1957385765610895</v>
+        <v>0.220910380820478</v>
       </c>
       <c r="E11" t="n">
-        <v>0.110178850663333</v>
+        <v>0.1380285064396777</v>
       </c>
       <c r="F11" t="n">
-        <v>2.287741977983852</v>
+        <v>2.665364200205063</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>279.6144261989056</v>
+        <v>5.442073267257953</v>
       </c>
       <c r="I11" t="n">
-        <v>1428.509551420176</v>
+        <v>24.63475571879274</v>
       </c>
       <c r="J11" t="n">
-        <v>3.148538508081721</v>
+        <v>0.07775425562506075</v>
       </c>
       <c r="K11" t="n">
-        <v>2.998094593880205</v>
+        <v>2.592923353215729</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1872062429018021</v>
+        <v>0.1732827965664991</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1090529970269752</v>
+        <v>0.09379075777481627</v>
       </c>
       <c r="F12" t="n">
-        <v>2.395373868433294</v>
+        <v>2.179876113387969</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H12" t="n">
-        <v>297.1734187283473</v>
+        <v>4.813087814210819</v>
       </c>
       <c r="I12" t="n">
-        <v>1587.411905297559</v>
+        <v>27.77591260978839</v>
       </c>
       <c r="J12" t="n">
-        <v>3.182679964833193</v>
+        <v>0.06142945338991258</v>
       </c>
       <c r="K12" t="n">
-        <v>3.002816124783307</v>
+        <v>2.456618154372967</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1855533092942547</v>
+        <v>0.1608079838998495</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1128348547669561</v>
+        <v>0.08588012531947897</v>
       </c>
       <c r="F13" t="n">
-        <v>2.551667393104422</v>
+        <v>2.146170822796978</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H13" t="n">
-        <v>322.213675565846</v>
+        <v>4.668490909465295</v>
       </c>
       <c r="I13" t="n">
-        <v>1736.501907680192</v>
+        <v>29.03146222125893</v>
       </c>
       <c r="J13" t="n">
-        <v>3.496796249403572</v>
+        <v>0.05909064790796022</v>
       </c>
       <c r="K13" t="n">
-        <v>2.946994335033697</v>
+        <v>2.48471451744543</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1836322074086295</v>
+        <v>0.1587813223226817</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1167168145732712</v>
+        <v>0.08982897169339321</v>
       </c>
       <c r="F14" t="n">
-        <v>2.74424462934032</v>
+        <v>2.302768808801672</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>340.2826863770684</v>
+        <v>4.771871627612771</v>
       </c>
       <c r="I14" t="n">
-        <v>1853.066470087412</v>
+        <v>30.05310421785747</v>
       </c>
       <c r="J14" t="n">
-        <v>3.23650330008993</v>
+        <v>0.05763865488867313</v>
       </c>
       <c r="K14" t="n">
-        <v>2.792322037809911</v>
+        <v>2.41337236841777</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1820496747200804</v>
+        <v>0.1565363205537034</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1200837409867532</v>
+        <v>0.09263755695928699</v>
       </c>
       <c r="F15" t="n">
-        <v>2.937899322287923</v>
+        <v>2.449755077379647</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H15" t="n">
-        <v>363.4077401702108</v>
+        <v>4.902376361705623</v>
       </c>
       <c r="I15" t="n">
-        <v>1996.200985961587</v>
+        <v>31.31782032671293</v>
       </c>
       <c r="J15" t="n">
-        <v>3.27864222049854</v>
+        <v>0.05510863415771602</v>
       </c>
       <c r="K15" t="n">
-        <v>2.660304767739412</v>
+        <v>2.466629573235681</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.187030223004006</v>
+        <v>0.1698314722247711</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1289609532185779</v>
+        <v>0.1105337202408262</v>
       </c>
       <c r="F16" t="n">
-        <v>3.220812379682086</v>
+        <v>2.864045710716884</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>400.1954253247525</v>
+        <v>5.684541315434748</v>
       </c>
       <c r="I16" t="n">
-        <v>2139.736663395737</v>
+        <v>33.47166011674965</v>
       </c>
       <c r="J16" t="n">
-        <v>3.496528633594149</v>
+        <v>0.05939408301049857</v>
       </c>
       <c r="K16" t="n">
-        <v>2.653530834533844</v>
+        <v>2.478110188168731</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1813837016213826</v>
+        <v>0.1621548794147148</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1268092817294748</v>
+        <v>0.1062985380423624</v>
       </c>
       <c r="F17" t="n">
-        <v>3.323602925704718</v>
+        <v>2.903070187389284</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>411.8469930799561</v>
+        <v>5.68860229104897</v>
       </c>
       <c r="I17" t="n">
-        <v>2270.584343568194</v>
+        <v>35.08128963853281</v>
       </c>
       <c r="J17" t="n">
-        <v>3.208763879884398</v>
+        <v>0.05793335700482313</v>
       </c>
       <c r="K17" t="n">
-        <v>2.68448070043624</v>
+        <v>2.5488342434203</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1786261047719352</v>
+        <v>0.1760182846762523</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1272902363201811</v>
+        <v>0.1245194274685182</v>
       </c>
       <c r="F18" t="n">
-        <v>3.479557474318562</v>
+        <v>3.417906614242644</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>424.6289780334126</v>
+        <v>6.677024809548607</v>
       </c>
       <c r="I18" t="n">
-        <v>2377.19441162067</v>
+        <v>37.93370002343538</v>
       </c>
       <c r="J18" t="n">
-        <v>3.120203280931098</v>
+        <v>0.06192438788961123</v>
       </c>
       <c r="K18" t="n">
-        <v>2.800440792812453</v>
+        <v>2.496025906832398</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1420228494023555</v>
+        <v>0.1680432063171179</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0909527809144004</v>
+        <v>0.1185219685978987</v>
       </c>
       <c r="F19" t="n">
-        <v>2.78094104055983</v>
+        <v>3.393356346824515</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>350.3795911848542</v>
+        <v>6.52794439671753</v>
       </c>
       <c r="I19" t="n">
-        <v>2467.064931166232</v>
+        <v>38.84682124190434</v>
       </c>
       <c r="J19" t="n">
-        <v>2.275645601996321</v>
+        <v>0.05820382803826164</v>
       </c>
       <c r="K19" t="n">
-        <v>2.999493467647497</v>
+        <v>2.379760607722123</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1506106118794473</v>
+        <v>0.1518696145162111</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1028921069288545</v>
+        <v>0.1042218400508297</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1562307334521</v>
+        <v>3.187339098629931</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>391.6978350121977</v>
+        <v>6.524546138190697</v>
       </c>
       <c r="I20" t="n">
-        <v>2600.731981128414</v>
+        <v>42.96149798611786</v>
       </c>
       <c r="J20" t="n">
-        <v>2.249069466210191</v>
+        <v>0.05666394658920708</v>
       </c>
       <c r="K20" t="n">
-        <v>2.88557007950668</v>
+        <v>2.65932001350066</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1585465687618328</v>
+        <v>0.1507250385435525</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1137884075257601</v>
+        <v>0.105550838466082</v>
       </c>
       <c r="F21" t="n">
-        <v>3.542294061759905</v>
+        <v>3.336529219888113</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>437.3574734654106</v>
+        <v>6.786013270099708</v>
       </c>
       <c r="I21" t="n">
-        <v>2758.542659616967</v>
+        <v>45.02246830170068</v>
       </c>
       <c r="J21" t="n">
-        <v>2.462287852711914</v>
+        <v>0.05181189220616852</v>
       </c>
       <c r="K21" t="n">
-        <v>2.924825480907717</v>
+        <v>2.865617766450951</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1603919149157114</v>
+        <v>0.1477638684982017</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1175547677175335</v>
+        <v>0.1042824332174977</v>
       </c>
       <c r="F22" t="n">
-        <v>3.744224940416515</v>
+        <v>3.398320859104109</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>454.795913949435</v>
+        <v>6.913888070677714</v>
       </c>
       <c r="I22" t="n">
-        <v>2835.528924188215</v>
+        <v>46.79011277213453</v>
       </c>
       <c r="J22" t="n">
-        <v>2.510511915425312</v>
+        <v>0.05086959754443176</v>
       </c>
       <c r="K22" t="n">
-        <v>3.038055256519332</v>
+        <v>2.51904335024632</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1734243663904889</v>
+        <v>0.1532917590494572</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1332993356327457</v>
+        <v>0.1121894172557416</v>
       </c>
       <c r="F23" t="n">
-        <v>4.322099276073995</v>
+        <v>3.729513997494292</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>516.9567542219174</v>
+        <v>7.499120744948797</v>
       </c>
       <c r="I23" t="n">
-        <v>2980.877283748686</v>
+        <v>48.92057336578231</v>
       </c>
       <c r="J23" t="n">
-        <v>2.986512648123567</v>
+        <v>0.05099524381818663</v>
       </c>
       <c r="K23" t="n">
-        <v>3.061696553839871</v>
+        <v>1.509970360782888</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1798123071961128</v>
+        <v>0.1423848718943397</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1418406547514884</v>
+        <v>0.102680467815374</v>
       </c>
       <c r="F24" t="n">
-        <v>4.735435400351363</v>
+        <v>3.586122879748021</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>558.5479332955125</v>
+        <v>7.361947968876994</v>
       </c>
       <c r="I24" t="n">
-        <v>3106.283112681106</v>
+        <v>51.70456573743391</v>
       </c>
       <c r="J24" t="n">
-        <v>2.917525536786429</v>
+        <v>0.0523375409027087</v>
       </c>
       <c r="K24" t="n">
-        <v>2.977156984734426</v>
+        <v>1.390299823157506</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1774324078179464</v>
+        <v>0.1447318717187747</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1407106403098188</v>
+        <v>0.1065502588490772</v>
       </c>
       <c r="F25" t="n">
-        <v>4.831804672219994</v>
+        <v>3.790617023243658</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>572.5149498853341</v>
+        <v>7.869324251712192</v>
       </c>
       <c r="I25" t="n">
-        <v>3226.665054744453</v>
+        <v>54.37174382020638</v>
       </c>
       <c r="J25" t="n">
-        <v>2.800064416538936</v>
+        <v>0.05415277350437812</v>
       </c>
       <c r="K25" t="n">
-        <v>3.00916528730861</v>
+        <v>1.341706332290278</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.156605801438998</v>
+        <v>0.1428848990607446</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1205633143210064</v>
+        <v>0.1062560485932549</v>
       </c>
       <c r="F26" t="n">
-        <v>4.345033152854322</v>
+        <v>3.900884063712674</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>527.0727437857944</v>
+        <v>8.008927530465822</v>
       </c>
       <c r="I26" t="n">
-        <v>3365.601650403116</v>
+        <v>56.05160225546993</v>
       </c>
       <c r="J26" t="n">
-        <v>2.374330964117689</v>
+        <v>0.05328860586854722</v>
       </c>
       <c r="K26" t="n">
-        <v>3.00054304097302</v>
+        <v>1.292607015409274</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1510789075224354</v>
+        <v>0.1520135534444001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1162870594700763</v>
+        <v>0.1172600105527771</v>
       </c>
       <c r="F27" t="n">
-        <v>4.342365122285905</v>
+        <v>4.374044796481503</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>524.2785896652176</v>
+        <v>9.049314736772013</v>
       </c>
       <c r="I27" t="n">
-        <v>3470.23021454773</v>
+        <v>59.52965726889514</v>
       </c>
       <c r="J27" t="n">
-        <v>2.226196750597478</v>
+        <v>0.05808340745296577</v>
       </c>
       <c r="K27" t="n">
-        <v>2.813430851515436</v>
+        <v>1.328976523251361</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1409591011057229</v>
+        <v>0.143579102046147</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1068701765464262</v>
+        <v>0.1095941457781369</v>
       </c>
       <c r="F28" t="n">
-        <v>4.135041011943001</v>
+        <v>4.224784075455696</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>515.6187497684589</v>
+        <v>8.767642089980598</v>
       </c>
       <c r="I28" t="n">
-        <v>3657.931596639026</v>
+        <v>61.06489012003038</v>
       </c>
       <c r="J28" t="n">
-        <v>2.135068889795818</v>
+        <v>0.05529828636220793</v>
       </c>
       <c r="K28" t="n">
-        <v>2.831015557243114</v>
+        <v>1.288284343822817</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1371493281783221</v>
+        <v>0.1386150175349834</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1042160964294032</v>
+        <v>0.1057377281279217</v>
       </c>
       <c r="F29" t="n">
-        <v>4.16446613025835</v>
+        <v>4.21613277842821</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>516.6151704486774</v>
+        <v>8.825663100849603</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.807882405171</v>
+        <v>63.67032416687606</v>
       </c>
       <c r="J29" t="n">
-        <v>2.048462958924018</v>
+        <v>0.05197112950933601</v>
       </c>
       <c r="K29" t="n">
-        <v>2.084169205880113</v>
+        <v>1.247691113549155</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1332413391931097</v>
+        <v>0.1419253266484997</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1013752119575622</v>
+        <v>0.1103784636576356</v>
       </c>
       <c r="F30" t="n">
-        <v>4.181284352761755</v>
+        <v>4.498872889187159</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>517.6688857552714</v>
+        <v>9.435524747991581</v>
       </c>
       <c r="I30" t="n">
-        <v>3885.197258525015</v>
+        <v>66.48231834871964</v>
       </c>
       <c r="J30" t="n">
-        <v>1.975789818515561</v>
+        <v>0.05633496025167525</v>
       </c>
       <c r="K30" t="n">
-        <v>1.772633004379448</v>
+        <v>1.222493011579532</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1233373656663249</v>
+        <v>0.1350811004516905</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09202798586869354</v>
+        <v>0.1041911397535366</v>
       </c>
       <c r="F31" t="n">
-        <v>3.939310406770056</v>
+        <v>4.372977413977852</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>492.0635335097292</v>
+        <v>9.299189211751184</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.573888264735</v>
+        <v>68.84152690980542</v>
       </c>
       <c r="J31" t="n">
-        <v>1.855851251144761</v>
+        <v>0.05397327770193271</v>
       </c>
       <c r="K31" t="n">
-        <v>1.542040751623355</v>
+        <v>1.184717535523545</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1199093233659921</v>
+        <v>0.1303144473093287</v>
       </c>
       <c r="E32" t="n">
-        <v>0.08956136899930212</v>
+        <v>0.1003252903199952</v>
       </c>
       <c r="F32" t="n">
-        <v>3.951150114341979</v>
+        <v>4.345385479014258</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>504.6563686789769</v>
+        <v>9.261743230341208</v>
       </c>
       <c r="I32" t="n">
-        <v>4208.649957423613</v>
+        <v>71.07226728557976</v>
       </c>
       <c r="J32" t="n">
-        <v>1.796318003689978</v>
+        <v>0.05191841638171241</v>
       </c>
       <c r="K32" t="n">
-        <v>1.298371242757974</v>
+        <v>1.16159442470981</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1199823590229409</v>
+        <v>0.1347227984265004</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09064843765703878</v>
+        <v>0.1058802250407169</v>
       </c>
       <c r="F33" t="n">
-        <v>4.090225698989209</v>
+        <v>4.670970118529927</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>521.328086874253</v>
+        <v>9.987994536717501</v>
       </c>
       <c r="I33" t="n">
-        <v>4345.039480133692</v>
+        <v>74.13737432248017</v>
       </c>
       <c r="J33" t="n">
-        <v>1.807282539261265</v>
+        <v>0.0530614622826294</v>
       </c>
       <c r="K33" t="n">
-        <v>1.211689882701069</v>
+        <v>1.171534160179125</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1176038400161104</v>
+        <v>0.1342487022391784</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08895461404260741</v>
+        <v>0.1061398938703205</v>
       </c>
       <c r="F34" t="n">
-        <v>4.10495697597135</v>
+        <v>4.776036766749404</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>520.7155688374834</v>
+        <v>10.16493004888118</v>
       </c>
       <c r="I34" t="n">
-        <v>4427.708897652928</v>
+        <v>75.71715688373116</v>
       </c>
       <c r="J34" t="n">
-        <v>1.727750284267187</v>
+        <v>0.0525684985520492</v>
       </c>
       <c r="K34" t="n">
-        <v>1.20471202793636</v>
+        <v>1.151473599172981</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1123462376293862</v>
+        <v>0.1425374227595327</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08443259730326635</v>
+        <v>0.1155731907708387</v>
       </c>
       <c r="F35" t="n">
-        <v>4.024779151584153</v>
+        <v>5.286166608390639</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>512.1860879232298</v>
+        <v>11.15910428444386</v>
       </c>
       <c r="I35" t="n">
-        <v>4558.996355648836</v>
+        <v>78.28894383245442</v>
       </c>
       <c r="J35" t="n">
-        <v>1.638512959182266</v>
+        <v>0.05508540974922654</v>
       </c>
       <c r="K35" t="n">
-        <v>1.161058937096365</v>
+        <v>1.12699127796414</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1066976656830323</v>
+        <v>0.1438028889081328</v>
       </c>
       <c r="E36" t="n">
-        <v>0.07946283841727109</v>
+        <v>0.117699318448015</v>
       </c>
       <c r="F36" t="n">
-        <v>3.917692028734449</v>
+        <v>5.508935612001458</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>501.1435871245986</v>
+        <v>11.61691175804159</v>
       </c>
       <c r="I36" t="n">
-        <v>4696.856148787268</v>
+        <v>80.78357706334363</v>
       </c>
       <c r="J36" t="n">
-        <v>1.548208442998378</v>
+        <v>0.05630485949292613</v>
       </c>
       <c r="K36" t="n">
-        <v>1.160780826679775</v>
+        <v>1.102539737635598</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1080088036130917</v>
+        <v>0.1499140781619722</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08146144657776722</v>
+        <v>0.1246139019167929</v>
       </c>
       <c r="F37" t="n">
-        <v>4.068533205372278</v>
+        <v>5.925416357150332</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>517.6119870815246</v>
+        <v>12.47454085356745</v>
       </c>
       <c r="I37" t="n">
-        <v>4792.312939005513</v>
+        <v>83.21127012560841</v>
       </c>
       <c r="J37" t="n">
-        <v>1.611947160650189</v>
+        <v>0.06034179433312591</v>
       </c>
       <c r="K37" t="n">
-        <v>1.139817896968758</v>
+        <v>1.093745481262665</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1113424401543734</v>
+        <v>0.1373870677503542</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0856586956501646</v>
+        <v>0.1124560581477633</v>
       </c>
       <c r="F38" t="n">
-        <v>4.33513268036627</v>
+        <v>5.510690098008564</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>547.2909852456004</v>
+        <v>11.84807686499018</v>
       </c>
       <c r="I38" t="n">
-        <v>4915.385224958205</v>
+        <v>86.23866175322485</v>
       </c>
       <c r="J38" t="n">
-        <v>1.673314511431523</v>
+        <v>0.05517502891479707</v>
       </c>
       <c r="K38" t="n">
-        <v>1.116026307197824</v>
+        <v>1.075456417574971</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.111592839085477</v>
+        <v>0.1284931468947918</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08663758175641745</v>
+        <v>0.1040126173131849</v>
       </c>
       <c r="F39" t="n">
-        <v>4.471716625239145</v>
+        <v>5.248789511127772</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>560.2272890045764</v>
+        <v>11.3447709148358</v>
       </c>
       <c r="I39" t="n">
-        <v>5020.279917562256</v>
+        <v>88.29086366858712</v>
       </c>
       <c r="J39" t="n">
-        <v>1.687716680129022</v>
+        <v>0.05200315362040127</v>
       </c>
       <c r="K39" t="n">
-        <v>1.091388283494853</v>
+        <v>1.069226679063282</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1089089160097484</v>
+        <v>0.1203777563461779</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08442839172430217</v>
+        <v>0.09621231009195219</v>
       </c>
       <c r="F40" t="n">
-        <v>4.448798348428108</v>
+        <v>4.981400098296432</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>552.4494050806063</v>
+        <v>10.97414031212789</v>
       </c>
       <c r="I40" t="n">
-        <v>5072.581982462818</v>
+        <v>91.16418718229689</v>
       </c>
       <c r="J40" t="n">
-        <v>1.614175829568016</v>
+        <v>0.04806577108247118</v>
       </c>
       <c r="K40" t="n">
-        <v>1.074859022513503</v>
+        <v>1.061724624311823</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1040828811823579</v>
+        <v>0.1160396897765592</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08012787800541543</v>
+        <v>0.09240438736416767</v>
       </c>
       <c r="F41" t="n">
-        <v>4.344932889950189</v>
+        <v>4.9095919210969</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>537.4083875266838</v>
+        <v>10.76113288586541</v>
       </c>
       <c r="I41" t="n">
-        <v>5163.273551057066</v>
+        <v>92.73665679895012</v>
       </c>
       <c r="J41" t="n">
-        <v>1.471063587322091</v>
+        <v>0.04681604214995268</v>
       </c>
       <c r="K41" t="n">
-        <v>1.050560511518198</v>
+        <v>1.055373750875181</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1021715403532957</v>
+        <v>0.1167195422117269</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0787905908833294</v>
+        <v>0.09371744695682382</v>
       </c>
       <c r="F42" t="n">
-        <v>4.369862758761745</v>
+        <v>5.07430044603645</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>542.4299805311384</v>
+        <v>10.96402087779252</v>
       </c>
       <c r="I42" t="n">
-        <v>5309.012457436651</v>
+        <v>93.93474880071071</v>
       </c>
       <c r="J42" t="n">
-        <v>1.423972508892905</v>
+        <v>0.04750565602582495</v>
       </c>
       <c r="K42" t="n">
-        <v>1.03969915017709</v>
+        <v>1.03992929603375</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1009978679354605</v>
+        <v>0.1181844873080775</v>
       </c>
       <c r="E43" t="n">
-        <v>0.07806414007667117</v>
+        <v>0.09568919361695705</v>
       </c>
       <c r="F43" t="n">
-        <v>4.403901038563748</v>
+        <v>5.253742801976764</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>546.4703511213537</v>
+        <v>11.266917637407</v>
       </c>
       <c r="I43" t="n">
-        <v>5410.711753544724</v>
+        <v>95.33330383738904</v>
       </c>
       <c r="J43" t="n">
-        <v>1.431999048437624</v>
+        <v>0.0484491832108743</v>
       </c>
       <c r="K43" t="n">
-        <v>1.030403677345303</v>
+        <v>1.034862878507022</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1024184170437842</v>
+        <v>0.1142857634029291</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08009051697024649</v>
+        <v>0.09225307095026569</v>
       </c>
       <c r="F44" t="n">
-        <v>4.587015201002585</v>
+        <v>5.187099291131509</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>571.6890525071926</v>
+        <v>11.0917276744835</v>
       </c>
       <c r="I44" t="n">
-        <v>5581.896977208637</v>
+        <v>97.05257544089891</v>
       </c>
       <c r="J44" t="n">
-        <v>1.555831228381339</v>
+        <v>0.04660158778640208</v>
       </c>
       <c r="K44" t="n">
-        <v>1.021585793227866</v>
+        <v>1.046335461079806</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1050226306919052</v>
+        <v>0.1096975526298287</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08329987900966995</v>
+        <v>0.08808826992666918</v>
       </c>
       <c r="F45" t="n">
-        <v>4.834683571777502</v>
+        <v>5.076408788607769</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>599.146925295322</v>
+        <v>10.82165619264862</v>
       </c>
       <c r="I45" t="n">
-        <v>5704.931607102682</v>
+        <v>98.6499327762215</v>
       </c>
       <c r="J45" t="n">
-        <v>1.690887425291283</v>
+        <v>0.04462790626407206</v>
       </c>
       <c r="K45" t="n">
-        <v>1.014297727434942</v>
+        <v>1.03090999921904</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1041285559695659</v>
+        <v>0.1090099146180428</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08279828349265095</v>
+        <v>0.0877958649660916</v>
       </c>
       <c r="F46" t="n">
-        <v>4.881726479690312</v>
+        <v>5.138571673325731</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>598.5312414681146</v>
+        <v>10.90151701070066</v>
       </c>
       <c r="I46" t="n">
-        <v>5748.002897908714</v>
+        <v>100.0048211109807</v>
       </c>
       <c r="J46" t="n">
-        <v>1.689116962420007</v>
+        <v>0.0437960046230363</v>
       </c>
       <c r="K46" t="n">
-        <v>1.010550575605085</v>
+        <v>1.030838906046814</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09853654398171491</v>
+        <v>0.1158422797123078</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07757227756268503</v>
+        <v>0.09528047226375691</v>
       </c>
       <c r="F47" t="n">
-        <v>4.700214260407908</v>
+        <v>5.633856848536506</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>577.8523054740424</v>
+        <v>11.8499098485177</v>
       </c>
       <c r="I47" t="n">
-        <v>5864.345167020192</v>
+        <v>102.2934793578539</v>
       </c>
       <c r="J47" t="n">
-        <v>1.543697908365673</v>
+        <v>0.04651034347172527</v>
       </c>
       <c r="K47" t="n">
-        <v>1.009454205934032</v>
+        <v>1.019499280334781</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1012767690435419</v>
+        <v>0.1146399622707872</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08085124106725872</v>
+        <v>0.09451814323148688</v>
       </c>
       <c r="F48" t="n">
-        <v>4.958342773863092</v>
+        <v>5.697296156320747</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>602.8288628484206</v>
+        <v>11.88111615161155</v>
       </c>
       <c r="I48" t="n">
-        <v>5952.291611803357</v>
+        <v>103.6385211253609</v>
       </c>
       <c r="J48" t="n">
-        <v>1.590506438488747</v>
+        <v>0.04553845858395915</v>
       </c>
       <c r="K48" t="n">
-        <v>1.007412742971417</v>
+        <v>1.008443193196477</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1198969598251169</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1002518026783561</v>
       </c>
       <c r="F49" t="n">
-        <v>5.123658092243791</v>
+        <v>6.103130605136761</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>620.685904675744</v>
+        <v>12.5622873731696</v>
       </c>
       <c r="I49" t="n">
-        <v>6120.49474534301</v>
+        <v>104.7756956597823</v>
       </c>
       <c r="J49" t="n">
-        <v>1.574534992213807</v>
+        <v>0.0477961667173784</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>1.004401483699101</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6657181894367811</v>
+        <v>0.6389896638986157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3314363788735621</v>
+        <v>0.2779793277972313</v>
       </c>
       <c r="F2" t="n">
-        <v>1.991487925457673</v>
+        <v>1.770003792132878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.164</v>
+        <v>0.142</v>
       </c>
       <c r="H2" t="n">
-        <v>3.434911164195332</v>
+        <v>204.9368616785852</v>
       </c>
       <c r="I2" t="n">
-        <v>5.159707543970486</v>
+        <v>320.7201512904302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3019840033895965</v>
+        <v>15.52267919143591</v>
       </c>
       <c r="K2" t="n">
         <v>4.996943113347171</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4326010350126255</v>
+        <v>0.4456460273262675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1489015525189382</v>
+        <v>0.1684690409894012</v>
       </c>
       <c r="F3" t="n">
-        <v>1.524856623671322</v>
+        <v>1.607803134076408</v>
       </c>
       <c r="G3" t="n">
-        <v>0.173</v>
+        <v>0.091</v>
       </c>
       <c r="H3" t="n">
-        <v>3.41981054638972</v>
+        <v>214.3405644124759</v>
       </c>
       <c r="I3" t="n">
-        <v>7.905229691116926</v>
+        <v>480.965948913424</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1492332621922114</v>
+        <v>7.420789431727797</v>
       </c>
       <c r="K3" t="n">
         <v>3.402274237945569</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2652559831182226</v>
+        <v>0.3015093995100133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002847405660444946</v>
+        <v>0.05204847076358943</v>
       </c>
       <c r="F4" t="n">
-        <v>1.010851038819046</v>
+        <v>1.208643778507281</v>
       </c>
       <c r="G4" t="n">
-        <v>0.457</v>
+        <v>0.261</v>
       </c>
       <c r="H4" t="n">
-        <v>2.733920738517556</v>
+        <v>178.1416247964755</v>
       </c>
       <c r="I4" t="n">
-        <v>10.3067260024784</v>
+        <v>590.8327404915924</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06972885013094039</v>
+        <v>3.349990029263382</v>
       </c>
       <c r="K4" t="n">
         <v>3.532155939915008</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2668195994576067</v>
+        <v>0.2766423534527674</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07387738878855599</v>
+        <v>0.08628507804560093</v>
       </c>
       <c r="F5" t="n">
-        <v>1.382899048022602</v>
+        <v>1.453279644085264</v>
       </c>
       <c r="G5" t="n">
-        <v>0.157</v>
+        <v>0.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.330827788783898</v>
+        <v>192.9765953067935</v>
       </c>
       <c r="I5" t="n">
-        <v>12.48344497763595</v>
+        <v>697.5670677257358</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08710823726539786</v>
+        <v>3.230156169855928</v>
       </c>
       <c r="K5" t="n">
         <v>4.670193893916771</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2505151705239327</v>
+        <v>0.2435929635426625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09437249771641876</v>
+        <v>0.08600816428071734</v>
       </c>
       <c r="F6" t="n">
-        <v>1.604399143549676</v>
+        <v>1.54578972517362</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="H6" t="n">
-        <v>3.622972472842313</v>
+        <v>197.0847655248341</v>
       </c>
       <c r="I6" t="n">
-        <v>14.46208812530256</v>
+        <v>809.0741319394349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08645080993639284</v>
+        <v>3.10905180035944</v>
       </c>
       <c r="K6" t="n">
         <v>3.599385077299881</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2803470166906221</v>
+        <v>0.2478545176197106</v>
       </c>
       <c r="E7" t="n">
-        <v>0.151837555385376</v>
+        <v>0.1135428243375159</v>
       </c>
       <c r="F7" t="n">
-        <v>2.181528222460752</v>
+        <v>1.845368125163591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>4.601671985330138</v>
+        <v>229.3538091780372</v>
       </c>
       <c r="I7" t="n">
-        <v>16.41419994280991</v>
+        <v>925.3565816780495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1027831427396217</v>
+        <v>4.13244119522001</v>
       </c>
       <c r="K7" t="n">
         <v>3.498906026740482</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.255569169325842</v>
+        <v>0.233022470629634</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1427766192236968</v>
+        <v>0.1168137540583664</v>
       </c>
       <c r="F8" t="n">
-        <v>2.265833772659613</v>
+        <v>2.005206472500088</v>
       </c>
       <c r="G8" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>4.82768773238937</v>
+        <v>250.6842854742739</v>
       </c>
       <c r="I8" t="n">
-        <v>18.88994570481321</v>
+        <v>1075.794470794671</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0887526313465278</v>
+        <v>3.519603706878175</v>
       </c>
       <c r="K8" t="n">
         <v>2.844188637036549</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2346119028123378</v>
+        <v>0.2281878264065785</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1339029426560665</v>
+        <v>0.1266335930390231</v>
       </c>
       <c r="F9" t="n">
-        <v>2.329603070553877</v>
+        <v>2.246955334502874</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.852775128084438</v>
+        <v>274.3514733551461</v>
       </c>
       <c r="I9" t="n">
-        <v>20.6842665266054</v>
+        <v>1202.305476481969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07783701930729836</v>
+        <v>3.167555132235982</v>
       </c>
       <c r="K9" t="n">
         <v>3.032286700991945</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2435437357370023</v>
+        <v>0.2216839647562071</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1534894185628358</v>
+        <v>0.1290272938938508</v>
       </c>
       <c r="F10" t="n">
-        <v>2.704409331825648</v>
+        <v>2.392531079446227</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>5.552038514240758</v>
+        <v>291.447069548655</v>
       </c>
       <c r="I10" t="n">
-        <v>22.7968849103813</v>
+        <v>1314.696215710363</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08832746348937695</v>
+        <v>3.908484044632436</v>
       </c>
       <c r="K10" t="n">
         <v>2.729941736124553</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.220910380820478</v>
+        <v>0.2004315370585785</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1380285064396777</v>
+        <v>0.1153710622775762</v>
       </c>
       <c r="F11" t="n">
-        <v>2.665364200205063</v>
+        <v>2.356341621353653</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>5.442073267257953</v>
+        <v>284.6908446381564</v>
       </c>
       <c r="I11" t="n">
-        <v>24.63475571879274</v>
+        <v>1420.389469721784</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07775425562506075</v>
+        <v>3.34952752298524</v>
       </c>
       <c r="K11" t="n">
         <v>2.592923353215729</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1732827965664991</v>
+        <v>0.1658631746665973</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09379075777481627</v>
+        <v>0.08565771069223149</v>
       </c>
       <c r="F12" t="n">
-        <v>2.179876113387969</v>
+        <v>2.067978494826843</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="n">
-        <v>4.813087814210819</v>
+        <v>263.0101071229528</v>
       </c>
       <c r="I12" t="n">
-        <v>27.77591260978839</v>
+        <v>1585.705251642694</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06142945338991258</v>
+        <v>2.905296894684483</v>
       </c>
       <c r="K12" t="n">
         <v>2.456618154372967</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1608079838998495</v>
+        <v>0.1532880048433934</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08588012531947897</v>
+        <v>0.07768871956155365</v>
       </c>
       <c r="F13" t="n">
-        <v>2.146170822796978</v>
+        <v>2.02763828086369</v>
       </c>
       <c r="G13" t="n">
         <v>0.006</v>
       </c>
       <c r="H13" t="n">
-        <v>4.668490909465295</v>
+        <v>253.9143295433526</v>
       </c>
       <c r="I13" t="n">
-        <v>29.03146222125893</v>
+        <v>1656.452700279869</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05909064790796022</v>
+        <v>2.716206815600571</v>
       </c>
       <c r="K13" t="n">
         <v>2.48471451744543</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1587813223226817</v>
+        <v>0.147434450525499</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08982897169339321</v>
+        <v>0.07755202843742504</v>
       </c>
       <c r="F14" t="n">
-        <v>2.302768808801672</v>
+        <v>2.10975015061277</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.771871627612771</v>
+        <v>256.6961748534976</v>
       </c>
       <c r="I14" t="n">
-        <v>30.05310421785747</v>
+        <v>1741.086794426664</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05763865488867313</v>
+        <v>2.550367994940557</v>
       </c>
       <c r="K14" t="n">
         <v>2.41337236841777</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1565363205537034</v>
+        <v>0.1415347235548821</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09263755695928699</v>
+        <v>0.07649947533934287</v>
       </c>
       <c r="F15" t="n">
-        <v>2.449755077379647</v>
+        <v>2.176277133375567</v>
       </c>
       <c r="G15" t="n">
         <v>0.002</v>
       </c>
       <c r="H15" t="n">
-        <v>4.902376361705623</v>
+        <v>258.5114215704301</v>
       </c>
       <c r="I15" t="n">
-        <v>31.31782032671293</v>
+        <v>1826.487628459518</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05510863415771602</v>
+        <v>2.344694429684607</v>
       </c>
       <c r="K15" t="n">
         <v>2.466629573235681</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1698314722247711</v>
+        <v>0.1515499041561365</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1105337202408262</v>
+        <v>0.09094632588157481</v>
       </c>
       <c r="F16" t="n">
-        <v>2.864045710716884</v>
+        <v>2.500675842432055</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>5.684541315434748</v>
+        <v>293.0792017282699</v>
       </c>
       <c r="I16" t="n">
-        <v>33.47166011674965</v>
+        <v>1933.879162512177</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05939408301049857</v>
+        <v>2.538980198546303</v>
       </c>
       <c r="K16" t="n">
         <v>2.478110188168731</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1621548794147148</v>
+        <v>0.1480251875790986</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1062985380423624</v>
+        <v>0.09122686675103842</v>
       </c>
       <c r="F17" t="n">
-        <v>2.903070187389284</v>
+        <v>2.606154291553803</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>5.68860229104897</v>
+        <v>300.1435963045349</v>
       </c>
       <c r="I17" t="n">
-        <v>35.08128963853281</v>
+        <v>2027.652193611648</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05793335700482313</v>
+        <v>2.454486345193993</v>
       </c>
       <c r="K17" t="n">
         <v>2.5488342434203</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1760182846762523</v>
+        <v>0.1556481803633461</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1245194274685182</v>
+        <v>0.1028761916360552</v>
       </c>
       <c r="F18" t="n">
-        <v>3.417906614242644</v>
+        <v>2.94944693420002</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>6.677024809548607</v>
+        <v>342.4207628952841</v>
       </c>
       <c r="I18" t="n">
-        <v>37.93370002343538</v>
+        <v>2199.966373496529</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06192438788961123</v>
+        <v>2.742680176515577</v>
       </c>
       <c r="K18" t="n">
         <v>2.496025906832398</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1680432063171179</v>
+        <v>0.1482137806647556</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1185219685978987</v>
+        <v>0.09751221999003856</v>
       </c>
       <c r="F19" t="n">
-        <v>3.393356346824515</v>
+        <v>2.923258745734518</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>6.52794439671753</v>
+        <v>333.3384908766827</v>
       </c>
       <c r="I19" t="n">
-        <v>38.84682124190434</v>
+        <v>2249.038445558988</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05820382803826164</v>
+        <v>2.559302177750623</v>
       </c>
       <c r="K19" t="n">
         <v>2.379760607722123</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1518696145162111</v>
+        <v>0.1410883620088814</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1042218400508297</v>
+        <v>0.09283489920039167</v>
       </c>
       <c r="F20" t="n">
-        <v>3.187339098629931</v>
+        <v>2.923901287019303</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>6.524546138190697</v>
+        <v>354.2974623933246</v>
       </c>
       <c r="I20" t="n">
-        <v>42.96149798611786</v>
+        <v>2511.174255258714</v>
       </c>
       <c r="J20" t="n">
-        <v>0.05666394658920708</v>
+        <v>2.781699112013098</v>
       </c>
       <c r="K20" t="n">
         <v>2.65932001350066</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1507250385435525</v>
+        <v>0.1375485055887464</v>
       </c>
       <c r="E21" t="n">
-        <v>0.105550838466082</v>
+        <v>0.09167342609878626</v>
       </c>
       <c r="F21" t="n">
-        <v>3.336529219888113</v>
+        <v>2.998327351538403</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>6.786013270099708</v>
+        <v>364.4578244025018</v>
       </c>
       <c r="I21" t="n">
-        <v>45.02246830170068</v>
+        <v>2649.667641553207</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05181189220616852</v>
+        <v>2.475756938126526</v>
       </c>
       <c r="K21" t="n">
         <v>2.865617766450951</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1477638684982017</v>
+        <v>0.1388129725859854</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1042824332174977</v>
+        <v>0.09487485894241332</v>
       </c>
       <c r="F22" t="n">
-        <v>3.398320859104109</v>
+        <v>3.15928384436442</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>6.913888070677714</v>
+        <v>382.260555341772</v>
       </c>
       <c r="I22" t="n">
-        <v>46.79011277213453</v>
+        <v>2753.781208056667</v>
       </c>
       <c r="J22" t="n">
-        <v>0.05086959754443176</v>
+        <v>2.414512721311073</v>
       </c>
       <c r="K22" t="n">
         <v>2.51904335024632</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1532917590494572</v>
+        <v>0.1345348549718058</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1121894172557416</v>
+        <v>0.0925219838539324</v>
       </c>
       <c r="F23" t="n">
-        <v>3.729513997494292</v>
+        <v>3.202229492822515</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>7.499120744948797</v>
+        <v>388.9178272172028</v>
       </c>
       <c r="I23" t="n">
-        <v>48.92057336578231</v>
+        <v>2890.833214178641</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05099524381818663</v>
+        <v>2.263117479229881</v>
       </c>
       <c r="K23" t="n">
         <v>1.509970360782888</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1423848718943397</v>
+        <v>0.1360069661215136</v>
       </c>
       <c r="E24" t="n">
-        <v>0.102680467815374</v>
+        <v>0.09600728862713914</v>
       </c>
       <c r="F24" t="n">
-        <v>3.586122879748021</v>
+        <v>3.400201567641186</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>7.361947968876994</v>
+        <v>414.7564430778361</v>
       </c>
       <c r="I24" t="n">
-        <v>51.70456573743391</v>
+        <v>3049.523527399895</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0523375409027087</v>
+        <v>2.448733791435335</v>
       </c>
       <c r="K24" t="n">
         <v>1.390299823157506</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1447318717187747</v>
+        <v>0.136198915362837</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1065502588490772</v>
+        <v>0.09763636694153488</v>
       </c>
       <c r="F25" t="n">
-        <v>3.790617023243658</v>
+        <v>3.53189612560981</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>7.869324251712192</v>
+        <v>434.6410662895514</v>
       </c>
       <c r="I25" t="n">
-        <v>54.37174382020638</v>
+        <v>3191.22266966413</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05415277350437812</v>
+        <v>2.53409825265132</v>
       </c>
       <c r="K25" t="n">
         <v>1.341706332290278</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1428848990607446</v>
+        <v>0.1321583075968141</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1062560485932549</v>
+        <v>0.09507105578471209</v>
       </c>
       <c r="F26" t="n">
-        <v>3.900884063712674</v>
+        <v>3.563442992928623</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>8.008927530465822</v>
+        <v>435.5455898990688</v>
       </c>
       <c r="I26" t="n">
-        <v>56.05160225546993</v>
+        <v>3295.635346873709</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05328860586854722</v>
+        <v>2.476325744826906</v>
       </c>
       <c r="K26" t="n">
         <v>1.292607015409274</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1520135534444001</v>
+        <v>0.1457563002312957</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1172600105527771</v>
+        <v>0.1107463125358571</v>
       </c>
       <c r="F27" t="n">
-        <v>4.374044796481503</v>
+        <v>4.163277676623851</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>9.049314736772013</v>
+        <v>508.014426102324</v>
       </c>
       <c r="I27" t="n">
-        <v>59.52965726889514</v>
+        <v>3485.368559000011</v>
       </c>
       <c r="J27" t="n">
-        <v>0.05808340745296577</v>
+        <v>2.730080896926595</v>
       </c>
       <c r="K27" t="n">
         <v>1.328976523251361</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.143579102046147</v>
+        <v>0.1420514467776672</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1095941457781369</v>
+        <v>0.1080058692688445</v>
       </c>
       <c r="F28" t="n">
-        <v>4.224784075455696</v>
+        <v>4.172390576745403</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>8.767642089980598</v>
+        <v>503.9446283424147</v>
       </c>
       <c r="I28" t="n">
-        <v>61.06489012003038</v>
+        <v>3547.620526041999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.05529828636220793</v>
+        <v>2.623691073309471</v>
       </c>
       <c r="K28" t="n">
         <v>1.288284343822817</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1386150175349834</v>
+        <v>0.1364247552592991</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1057377281279217</v>
+        <v>0.1034638680554557</v>
       </c>
       <c r="F29" t="n">
-        <v>4.21613277842821</v>
+        <v>4.138989172700144</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>8.825663100849603</v>
+        <v>501.7543464260695</v>
       </c>
       <c r="I29" t="n">
-        <v>63.67032416687606</v>
+        <v>3677.883427185905</v>
       </c>
       <c r="J29" t="n">
-        <v>0.05197112950933601</v>
+        <v>2.413167830989561</v>
       </c>
       <c r="K29" t="n">
         <v>1.247691113549155</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1419253266484997</v>
+        <v>0.1385749954450141</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1103784636576356</v>
+        <v>0.1069049585128454</v>
       </c>
       <c r="F30" t="n">
-        <v>4.498872889187159</v>
+        <v>4.375586796498414</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>9.435524747991581</v>
+        <v>527.415003579189</v>
       </c>
       <c r="I30" t="n">
-        <v>66.48231834871964</v>
+        <v>3805.989687284276</v>
       </c>
       <c r="J30" t="n">
-        <v>0.05633496025167525</v>
+        <v>2.549222284304306</v>
       </c>
       <c r="K30" t="n">
         <v>1.222493011579532</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1350811004516905</v>
+        <v>0.1340293701835343</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1041911397535366</v>
+        <v>0.103101847690089</v>
       </c>
       <c r="F31" t="n">
-        <v>4.372977413977852</v>
+        <v>4.333660098766093</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>9.299189211751184</v>
+        <v>520.1773483970901</v>
       </c>
       <c r="I31" t="n">
-        <v>68.84152690980542</v>
+        <v>3881.069855694917</v>
       </c>
       <c r="J31" t="n">
-        <v>0.05397327770193271</v>
+        <v>2.413806199372829</v>
       </c>
       <c r="K31" t="n">
         <v>1.184717535523545</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1303144473093287</v>
+        <v>0.1293003964180958</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1003252903199952</v>
+        <v>0.0992762721566508</v>
       </c>
       <c r="F32" t="n">
-        <v>4.345385479014258</v>
+        <v>4.306550135889724</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>9.261743230341208</v>
+        <v>518.9017830358459</v>
       </c>
       <c r="I32" t="n">
-        <v>71.07226728557976</v>
+        <v>4013.149204569837</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05191841638171241</v>
+        <v>2.233092293451372</v>
       </c>
       <c r="K32" t="n">
         <v>1.16159442470981</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1347227984265004</v>
+        <v>0.1309758957012898</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1058802250407169</v>
+        <v>0.1020084255579993</v>
       </c>
       <c r="F33" t="n">
-        <v>4.670970118529927</v>
+        <v>4.521482029787382</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>9.987994536717501</v>
+        <v>547.3252115393125</v>
       </c>
       <c r="I33" t="n">
-        <v>74.13737432248017</v>
+        <v>4178.823963056301</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0530614622826294</v>
+        <v>2.177278759910908</v>
       </c>
       <c r="K33" t="n">
         <v>1.171534160179125</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1342487022391784</v>
+        <v>0.1282035112481497</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1061398938703205</v>
+        <v>0.09989843044451807</v>
       </c>
       <c r="F34" t="n">
-        <v>4.776036766749404</v>
+        <v>4.529346237785738</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>10.16493004888118</v>
+        <v>547.5123161406041</v>
       </c>
       <c r="I34" t="n">
-        <v>75.71715688373116</v>
+        <v>4270.649928462908</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0525684985520492</v>
+        <v>2.13242129921538</v>
       </c>
       <c r="K34" t="n">
         <v>1.151473599172981</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1425374227595327</v>
+        <v>0.1345982491857445</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1155731907708387</v>
+        <v>0.107384357650705</v>
       </c>
       <c r="F35" t="n">
-        <v>5.286166608390639</v>
+        <v>4.945939062498329</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>11.15910428444386</v>
+        <v>598.6203817281471</v>
       </c>
       <c r="I35" t="n">
-        <v>78.28894383245442</v>
+        <v>4447.460389340251</v>
       </c>
       <c r="J35" t="n">
-        <v>0.05508540974922654</v>
+        <v>2.162454452887919</v>
       </c>
       <c r="K35" t="n">
         <v>1.12699127796414</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1438028889081328</v>
+        <v>0.1344342009580813</v>
       </c>
       <c r="E36" t="n">
-        <v>0.117699318448015</v>
+        <v>0.1080449997677788</v>
       </c>
       <c r="F36" t="n">
-        <v>5.508935612001458</v>
+        <v>5.094288379122427</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>11.61691175804159</v>
+        <v>614.9969775852575</v>
       </c>
       <c r="I36" t="n">
-        <v>80.78357706334363</v>
+        <v>4574.706236971821</v>
       </c>
       <c r="J36" t="n">
-        <v>0.05630485949292613</v>
+        <v>2.221055835535509</v>
       </c>
       <c r="K36" t="n">
         <v>1.102539737635598</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1499140781619722</v>
+        <v>0.1379464757772148</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1246139019167929</v>
+        <v>0.1122901208896321</v>
       </c>
       <c r="F37" t="n">
-        <v>5.925416357150332</v>
+        <v>5.376698146780696</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>12.47454085356745</v>
+        <v>651.8955930844807</v>
       </c>
       <c r="I37" t="n">
-        <v>83.21127012560841</v>
+        <v>4725.714009086392</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06034179433312591</v>
+        <v>2.40650273850035</v>
       </c>
       <c r="K37" t="n">
         <v>1.093745481262665</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1373870677503542</v>
+        <v>0.1291953771568483</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1124560581477633</v>
+        <v>0.1040276134908612</v>
       </c>
       <c r="F38" t="n">
-        <v>5.510690098008564</v>
+        <v>5.133367385019165</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>11.84807686499018</v>
+        <v>630.3950869957489</v>
       </c>
       <c r="I38" t="n">
-        <v>86.23866175322485</v>
+        <v>4879.393526832037</v>
       </c>
       <c r="J38" t="n">
-        <v>0.05517502891479707</v>
+        <v>2.262627041043107</v>
       </c>
       <c r="K38" t="n">
         <v>1.075456417574971</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1284931468947918</v>
+        <v>0.121464893467048</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1040126173131849</v>
+        <v>0.09678694103634722</v>
       </c>
       <c r="F39" t="n">
-        <v>5.248789511127772</v>
+        <v>4.922000470182371</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>11.3447709148358</v>
+        <v>607.1900035559963</v>
       </c>
       <c r="I39" t="n">
-        <v>88.29086366858712</v>
+        <v>4998.892982363828</v>
       </c>
       <c r="J39" t="n">
-        <v>0.05200315362040127</v>
+        <v>2.075982907154741</v>
       </c>
       <c r="K39" t="n">
         <v>1.069226679063282</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1203777563461779</v>
+        <v>0.1139363680442187</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09621231009195219</v>
+        <v>0.08959396057290614</v>
       </c>
       <c r="F40" t="n">
-        <v>4.981400098296432</v>
+        <v>4.680571064242177</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>10.97414031212789</v>
+        <v>589.4154356199374</v>
       </c>
       <c r="I40" t="n">
-        <v>91.16418718229689</v>
+        <v>5173.198389044535</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04806577108247118</v>
+        <v>1.910400939725669</v>
       </c>
       <c r="K40" t="n">
         <v>1.061724624311823</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1160396897765592</v>
+        <v>0.1096830736851434</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09240438736416767</v>
+        <v>0.08587780827565517</v>
       </c>
       <c r="F41" t="n">
-        <v>4.9095919210969</v>
+        <v>4.607513161412881</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>10.76113288586541</v>
+        <v>579.1157120828823</v>
       </c>
       <c r="I41" t="n">
-        <v>92.73665679895012</v>
+        <v>5279.900468009256</v>
       </c>
       <c r="J41" t="n">
-        <v>0.04681604214995268</v>
+        <v>1.848383125923893</v>
       </c>
       <c r="K41" t="n">
         <v>1.055373750875181</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1167195422117269</v>
+        <v>0.1066404462175381</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09371744695682382</v>
+        <v>0.08337587450445305</v>
       </c>
       <c r="F42" t="n">
-        <v>5.07430044603645</v>
+        <v>4.583812998266335</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>10.96402087779252</v>
+        <v>569.6244447564569</v>
       </c>
       <c r="I42" t="n">
-        <v>93.93474880071071</v>
+        <v>5341.542209927255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.04750565602582495</v>
+        <v>1.813147073168272</v>
       </c>
       <c r="K42" t="n">
         <v>1.03992929603375</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1181844873080775</v>
+        <v>0.1081169200077596</v>
       </c>
       <c r="E43" t="n">
-        <v>0.09568919361695705</v>
+        <v>0.08536480062020246</v>
       </c>
       <c r="F43" t="n">
-        <v>5.253742801976764</v>
+        <v>4.751949397157583</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>11.266917637407</v>
+        <v>586.2306873424116</v>
       </c>
       <c r="I43" t="n">
-        <v>95.33330383738904</v>
+        <v>5422.191894666788</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0484491832108743</v>
+        <v>1.828783662473239</v>
       </c>
       <c r="K43" t="n">
         <v>1.034862878507022</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1142857634029291</v>
+        <v>0.1043571600106309</v>
       </c>
       <c r="E44" t="n">
-        <v>0.09225307095026569</v>
+        <v>0.08207748737407938</v>
       </c>
       <c r="F44" t="n">
-        <v>5.187099291131509</v>
+        <v>4.683962898064542</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>11.0917276744835</v>
+        <v>577.0079984698026</v>
       </c>
       <c r="I44" t="n">
-        <v>97.05257544089891</v>
+        <v>5529.165400927186</v>
       </c>
       <c r="J44" t="n">
-        <v>0.04660158778640208</v>
+        <v>1.749791547851857</v>
       </c>
       <c r="K44" t="n">
         <v>1.046335461079806</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1096975526298287</v>
+        <v>0.09601556918796182</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08808826992666918</v>
+        <v>0.07407419950805805</v>
       </c>
       <c r="F45" t="n">
-        <v>5.076408788607769</v>
+        <v>4.376006174122426</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>10.82165619264862</v>
+        <v>544.0133733480424</v>
       </c>
       <c r="I45" t="n">
-        <v>98.6499327762215</v>
+        <v>5665.887084240181</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04462790626407206</v>
+        <v>1.547169398511505</v>
       </c>
       <c r="K45" t="n">
         <v>1.03090999921904</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1090099146180428</v>
+        <v>0.09633975296739716</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0877958649660916</v>
+        <v>0.07482403279995431</v>
       </c>
       <c r="F46" t="n">
-        <v>5.138571673325731</v>
+        <v>4.477644820514824</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>10.90151701070066</v>
+        <v>555.28812656123</v>
       </c>
       <c r="I46" t="n">
-        <v>100.0048211109807</v>
+        <v>5763.852505923987</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0437960046230363</v>
+        <v>1.524658062332032</v>
       </c>
       <c r="K46" t="n">
         <v>1.030838906046814</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1158422797123078</v>
+        <v>0.09655837130762868</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09528047226375691</v>
+        <v>0.0755481008729223</v>
       </c>
       <c r="F47" t="n">
-        <v>5.633856848536506</v>
+        <v>4.595770035788138</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>11.8499098485177</v>
+        <v>568.2926754050744</v>
       </c>
       <c r="I47" t="n">
-        <v>102.2934793578539</v>
+        <v>5885.483233706697</v>
       </c>
       <c r="J47" t="n">
-        <v>0.04651034347172527</v>
+        <v>1.514057487768083</v>
       </c>
       <c r="K47" t="n">
         <v>1.019499280334781</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1146399622707872</v>
+        <v>0.09412845847468054</v>
       </c>
       <c r="E48" t="n">
-        <v>0.09451814323148688</v>
+        <v>0.07354046889455967</v>
       </c>
       <c r="F48" t="n">
-        <v>5.697296156320747</v>
+        <v>4.57200826279648</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>11.88111615161155</v>
+        <v>564.2783047438895</v>
       </c>
       <c r="I48" t="n">
-        <v>103.6385211253609</v>
+        <v>5994.768361108068</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04553845858395915</v>
+        <v>1.42949949753762</v>
       </c>
       <c r="K48" t="n">
         <v>1.008443193196477</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1198969598251169</v>
+        <v>0.09581462343086448</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1002518026783561</v>
+        <v>0.07563191413244619</v>
       </c>
       <c r="F49" t="n">
-        <v>6.103130605136761</v>
+        <v>4.747361814222526</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>12.5622873731696</v>
+        <v>580.3839552400905</v>
       </c>
       <c r="I49" t="n">
-        <v>104.7756956597823</v>
+        <v>6057.363004289939</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0477961667173784</v>
+        <v>1.468911117005158</v>
       </c>
       <c r="K49" t="n">
         <v>1.004401483699101</v>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -488,31 +488,31 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6389896638986157</v>
+        <v>0.3902551118339467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2779793277972313</v>
+        <v>0.05150795174169498</v>
       </c>
       <c r="F2" t="n">
-        <v>1.770003792132878</v>
+        <v>1.152054268817096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.142</v>
+        <v>0.347</v>
       </c>
       <c r="H2" t="n">
-        <v>204.9368616785852</v>
+        <v>122.0619721893547</v>
       </c>
       <c r="I2" t="n">
-        <v>320.7201512904302</v>
+        <v>312.7748195680061</v>
       </c>
       <c r="J2" t="n">
-        <v>15.52267919143591</v>
+        <v>5.084730382237121</v>
       </c>
       <c r="K2" t="n">
-        <v>4.996943113347171</v>
+        <v>3.05801854132884</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +523,31 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4456460273262675</v>
+        <v>0.285841571444759</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1684690409894012</v>
+        <v>0.04778876192634551</v>
       </c>
       <c r="F3" t="n">
-        <v>1.607803134076408</v>
+        <v>1.200748573490996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.091</v>
+        <v>0.269</v>
       </c>
       <c r="H3" t="n">
-        <v>214.3405644124759</v>
+        <v>128.3256227886046</v>
       </c>
       <c r="I3" t="n">
-        <v>480.965948913424</v>
+        <v>448.9396771085287</v>
       </c>
       <c r="J3" t="n">
-        <v>7.420789431727797</v>
+        <v>4.061832316873462</v>
       </c>
       <c r="K3" t="n">
-        <v>3.402274237945569</v>
+        <v>3.111508302276199</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3015093995100133</v>
+        <v>0.2879157375982248</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05204847076358943</v>
+        <v>0.118371865597802</v>
       </c>
       <c r="F4" t="n">
-        <v>1.208643778507281</v>
+        <v>1.698178378263692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.261</v>
+        <v>0.024</v>
       </c>
       <c r="H4" t="n">
-        <v>178.1416247964755</v>
+        <v>156.9833392121839</v>
       </c>
       <c r="I4" t="n">
-        <v>590.8327404915924</v>
+        <v>545.2405642071851</v>
       </c>
       <c r="J4" t="n">
-        <v>3.349990029263382</v>
+        <v>3.149159078476893</v>
       </c>
       <c r="K4" t="n">
-        <v>3.532155939915008</v>
+        <v>3.198313803284687</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2766423534527674</v>
+        <v>0.2791386690823043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08628507804560093</v>
+        <v>0.1504134314184301</v>
       </c>
       <c r="F5" t="n">
-        <v>1.453279644085264</v>
+        <v>2.168484394732194</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08</v>
+        <v>0.005</v>
       </c>
       <c r="H5" t="n">
-        <v>192.9765953067935</v>
+        <v>215.2169192747143</v>
       </c>
       <c r="I5" t="n">
-        <v>697.5670677257358</v>
+        <v>771.0036018379717</v>
       </c>
       <c r="J5" t="n">
-        <v>3.230156169855928</v>
+        <v>3.442725468488121</v>
       </c>
       <c r="K5" t="n">
-        <v>4.670193893916771</v>
+        <v>3.570574357503849</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2435929635426625</v>
+        <v>0.2215351826320979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08600816428071734</v>
+        <v>0.1070550624309359</v>
       </c>
       <c r="F6" t="n">
-        <v>1.54578972517362</v>
+        <v>1.935141072902621</v>
       </c>
       <c r="G6" t="n">
-        <v>0.052</v>
+        <v>0.013</v>
       </c>
       <c r="H6" t="n">
-        <v>197.0847655248341</v>
+        <v>206.7618655204346</v>
       </c>
       <c r="I6" t="n">
-        <v>809.0741319394349</v>
+        <v>933.3139010420878</v>
       </c>
       <c r="J6" t="n">
-        <v>3.10905180035944</v>
+        <v>2.616430655873559</v>
       </c>
       <c r="K6" t="n">
-        <v>3.599385077299881</v>
+        <v>2.839884339308284</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2478545176197106</v>
+        <v>0.1442630508228531</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1135428243375159</v>
+        <v>0.0372959321757097</v>
       </c>
       <c r="F7" t="n">
-        <v>1.845368125163591</v>
+        <v>1.348667260064649</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018</v>
+        <v>0.138</v>
       </c>
       <c r="H7" t="n">
-        <v>229.3538091780372</v>
+        <v>178.1550630549485</v>
       </c>
       <c r="I7" t="n">
-        <v>925.3565816780495</v>
+        <v>1234.932035880156</v>
       </c>
       <c r="J7" t="n">
-        <v>4.13244119522001</v>
+        <v>2.239931281329944</v>
       </c>
       <c r="K7" t="n">
-        <v>3.498906026740482</v>
+        <v>1.989662537849751</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.233022470629634</v>
+        <v>0.1238569898220696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1168137540583664</v>
+        <v>0.02862405393316414</v>
       </c>
       <c r="F8" t="n">
-        <v>2.005206472500088</v>
+        <v>1.300568849064526</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.196</v>
       </c>
       <c r="H8" t="n">
-        <v>250.6842854742739</v>
+        <v>169.2648005522443</v>
       </c>
       <c r="I8" t="n">
-        <v>1075.794470794671</v>
+        <v>1366.614841805914</v>
       </c>
       <c r="J8" t="n">
-        <v>3.519603706878175</v>
+        <v>2.075408200513311</v>
       </c>
       <c r="K8" t="n">
-        <v>2.844188637036549</v>
+        <v>1.588741709231285</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2281878264065785</v>
+        <v>0.1331300205454433</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1266335930390231</v>
+        <v>0.04977713790558203</v>
       </c>
       <c r="F9" t="n">
-        <v>2.246955334502874</v>
+        <v>1.597185560104162</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>274.3514733551461</v>
+        <v>207.6005435731717</v>
       </c>
       <c r="I9" t="n">
-        <v>1202.305476481969</v>
+        <v>1559.381893900544</v>
       </c>
       <c r="J9" t="n">
-        <v>3.167555132235982</v>
+        <v>2.4791546764683</v>
       </c>
       <c r="K9" t="n">
-        <v>3.032286700991945</v>
+        <v>1.492846890595561</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2216839647562071</v>
+        <v>0.1201749142244229</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1290272938938508</v>
+        <v>0.0456134662773402</v>
       </c>
       <c r="F10" t="n">
-        <v>2.392531079446227</v>
+        <v>1.611756712526728</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.063</v>
       </c>
       <c r="H10" t="n">
-        <v>291.447069548655</v>
+        <v>211.6889954908883</v>
       </c>
       <c r="I10" t="n">
-        <v>1314.696215710363</v>
+        <v>1761.507356648207</v>
       </c>
       <c r="J10" t="n">
-        <v>3.908484044632436</v>
+        <v>2.128364917438009</v>
       </c>
       <c r="K10" t="n">
-        <v>2.729941736124553</v>
+        <v>1.305323814555845</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2004315370585785</v>
+        <v>0.1093878897908734</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1153710622775762</v>
+        <v>0.040879265928633</v>
       </c>
       <c r="F11" t="n">
-        <v>2.356341621353653</v>
+        <v>1.596702482461688</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.051</v>
       </c>
       <c r="H11" t="n">
-        <v>284.6908446381564</v>
+        <v>205.6739559649264</v>
       </c>
       <c r="I11" t="n">
-        <v>1420.389469721784</v>
+        <v>1880.226013666884</v>
       </c>
       <c r="J11" t="n">
-        <v>3.34952752298524</v>
+        <v>2.044150312386404</v>
       </c>
       <c r="K11" t="n">
-        <v>2.592923353215729</v>
+        <v>1.531242495564548</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1658631746665973</v>
+        <v>0.1126380981254764</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08565771069223149</v>
+        <v>0.05014782334558043</v>
       </c>
       <c r="F12" t="n">
-        <v>2.067978494826843</v>
+        <v>1.802490043806202</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="H12" t="n">
-        <v>263.0101071229528</v>
+        <v>227.7034650697627</v>
       </c>
       <c r="I12" t="n">
-        <v>1585.705251642694</v>
+        <v>2021.549270266496</v>
       </c>
       <c r="J12" t="n">
-        <v>2.905296894684483</v>
+        <v>1.82863220919355</v>
       </c>
       <c r="K12" t="n">
-        <v>2.456618154372967</v>
+        <v>1.477087136409038</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1532880048433934</v>
+        <v>0.1105716531982852</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07768871956155365</v>
+        <v>0.05281656574362847</v>
       </c>
       <c r="F13" t="n">
-        <v>2.02763828086369</v>
+        <v>1.914492005316316</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H13" t="n">
-        <v>253.9143295433526</v>
+        <v>248.6133105126329</v>
       </c>
       <c r="I13" t="n">
-        <v>1656.452700279869</v>
+        <v>2248.436225031395</v>
       </c>
       <c r="J13" t="n">
-        <v>2.716206815600571</v>
+        <v>1.899022449669885</v>
       </c>
       <c r="K13" t="n">
-        <v>2.48471451744543</v>
+        <v>1.602580235453608</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.147434450525499</v>
+        <v>0.1001002216549968</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07755202843742504</v>
+        <v>0.04588939163421335</v>
       </c>
       <c r="F14" t="n">
-        <v>2.10975015061277</v>
+        <v>1.846498598464927</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="H14" t="n">
-        <v>256.6961748534976</v>
+        <v>241.6826553952741</v>
       </c>
       <c r="I14" t="n">
-        <v>1741.086794426664</v>
+        <v>2414.406795503932</v>
       </c>
       <c r="J14" t="n">
-        <v>2.550367994940557</v>
+        <v>1.662474314128731</v>
       </c>
       <c r="K14" t="n">
-        <v>2.41337236841777</v>
+        <v>1.715434961372016</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1415347235548821</v>
+        <v>0.1111902380761392</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07649947533934287</v>
+        <v>0.06181191796925811</v>
       </c>
       <c r="F15" t="n">
-        <v>2.176277133375567</v>
+        <v>2.251802771650878</v>
       </c>
       <c r="G15" t="n">
         <v>0.002</v>
       </c>
       <c r="H15" t="n">
-        <v>258.5114215704301</v>
+        <v>287.2023491648429</v>
       </c>
       <c r="I15" t="n">
-        <v>1826.487628459518</v>
+        <v>2582.981690966221</v>
       </c>
       <c r="J15" t="n">
-        <v>2.344694429684607</v>
+        <v>1.745200153297574</v>
       </c>
       <c r="K15" t="n">
-        <v>2.466629573235681</v>
+        <v>1.659856070261798</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1515499041561365</v>
+        <v>0.1060478296695005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09094632588157481</v>
+        <v>0.05948782079812043</v>
       </c>
       <c r="F16" t="n">
-        <v>2.500675842432055</v>
+        <v>2.277659137962208</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H16" t="n">
-        <v>293.0792017282699</v>
+        <v>289.4739106346469</v>
       </c>
       <c r="I16" t="n">
-        <v>1933.879162512177</v>
+        <v>2729.654265785507</v>
       </c>
       <c r="J16" t="n">
-        <v>2.538980198546303</v>
+        <v>1.60965813271052</v>
       </c>
       <c r="K16" t="n">
-        <v>2.478110188168731</v>
+        <v>1.858737118002542</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1480251875790986</v>
+        <v>0.1025326218239311</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09122686675103842</v>
+        <v>0.05853912289373153</v>
       </c>
       <c r="F17" t="n">
-        <v>2.606154291553803</v>
+        <v>2.330631214093938</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H17" t="n">
-        <v>300.1435963045349</v>
+        <v>300.1370712832941</v>
       </c>
       <c r="I17" t="n">
-        <v>2027.652193611648</v>
+        <v>2927.234922351728</v>
       </c>
       <c r="J17" t="n">
-        <v>2.454486345193993</v>
+        <v>1.613642578379915</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5488342434203</v>
+        <v>1.859498968539945</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1556481803633461</v>
+        <v>0.10496574440099</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1028761916360552</v>
+        <v>0.06352897330844332</v>
       </c>
       <c r="F18" t="n">
-        <v>2.94944693420002</v>
+        <v>2.533154529983883</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>342.4207628952841</v>
+        <v>325.0013862782683</v>
       </c>
       <c r="I18" t="n">
-        <v>2199.966373496529</v>
+        <v>3096.261433984581</v>
       </c>
       <c r="J18" t="n">
-        <v>2.742680176515577</v>
+        <v>1.736267353296915</v>
       </c>
       <c r="K18" t="n">
-        <v>2.496025906832398</v>
+        <v>1.905528612781861</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1482137806647556</v>
+        <v>0.09580553594699841</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09751221999003856</v>
+        <v>0.05614788401484927</v>
       </c>
       <c r="F19" t="n">
-        <v>2.923258745734518</v>
+        <v>2.415814635493633</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H19" t="n">
-        <v>333.3384908766827</v>
+        <v>314.8455803023907</v>
       </c>
       <c r="I19" t="n">
-        <v>2249.038445558988</v>
+        <v>3286.298408440298</v>
       </c>
       <c r="J19" t="n">
-        <v>2.559302177750623</v>
+        <v>1.520807982666343</v>
       </c>
       <c r="K19" t="n">
-        <v>2.379760607722123</v>
+        <v>1.98413360630721</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1410883620088814</v>
+        <v>0.09822262083449904</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09283489920039167</v>
+        <v>0.06095909276980882</v>
       </c>
       <c r="F20" t="n">
-        <v>2.923901287019303</v>
+        <v>2.635891605968788</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>354.2974623933246</v>
+        <v>340.5774747173907</v>
       </c>
       <c r="I20" t="n">
-        <v>2511.174255258714</v>
+        <v>3467.403657363708</v>
       </c>
       <c r="J20" t="n">
-        <v>2.781699112013098</v>
+        <v>1.478859384748739</v>
       </c>
       <c r="K20" t="n">
-        <v>2.65932001350066</v>
+        <v>1.843060346625855</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1375485055887464</v>
+        <v>0.1010914950295502</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09167342609878626</v>
+        <v>0.06570139640866646</v>
       </c>
       <c r="F21" t="n">
-        <v>2.998327351538403</v>
+        <v>2.85649091042362</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>364.4578244025018</v>
+        <v>361.3446443966353</v>
       </c>
       <c r="I21" t="n">
-        <v>2649.667641553207</v>
+        <v>3574.431699630222</v>
       </c>
       <c r="J21" t="n">
-        <v>2.475756938126526</v>
+        <v>1.460803219529729</v>
       </c>
       <c r="K21" t="n">
-        <v>2.865617766450951</v>
+        <v>1.90676609152101</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1388129725859854</v>
+        <v>0.1008193867733274</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09487485894241332</v>
+        <v>0.0670156043211968</v>
       </c>
       <c r="F22" t="n">
-        <v>3.15928384436442</v>
+        <v>2.98248833295793</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>382.260555341772</v>
+        <v>374.9606772598279</v>
       </c>
       <c r="I22" t="n">
-        <v>2753.781208056667</v>
+        <v>3719.132691243733</v>
       </c>
       <c r="J22" t="n">
-        <v>2.414512721311073</v>
+        <v>1.45164685760238</v>
       </c>
       <c r="K22" t="n">
-        <v>2.51904335024632</v>
+        <v>1.976275763327762</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1345348549718058</v>
+        <v>0.0997576773725929</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0925219838539324</v>
+        <v>0.06737486001189474</v>
       </c>
       <c r="F23" t="n">
-        <v>3.202229492822515</v>
+        <v>3.080574375646059</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>388.9178272172028</v>
+        <v>380.88809235367</v>
       </c>
       <c r="I23" t="n">
-        <v>2890.833214178641</v>
+        <v>3818.133124040776</v>
       </c>
       <c r="J23" t="n">
-        <v>2.263117479229881</v>
+        <v>1.354262012013912</v>
       </c>
       <c r="K23" t="n">
-        <v>1.509970360782888</v>
+        <v>1.922732074176519</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1360069661215136</v>
+        <v>0.1044499755888136</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09600728862713914</v>
+        <v>0.07356894026428995</v>
       </c>
       <c r="F24" t="n">
-        <v>3.400201567641186</v>
+        <v>3.38233399531998</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>414.7564430778361</v>
+        <v>411.0598811792544</v>
       </c>
       <c r="I24" t="n">
-        <v>3049.523527399895</v>
+        <v>3935.471299653211</v>
       </c>
       <c r="J24" t="n">
-        <v>2.448733791435335</v>
+        <v>1.438157829846628</v>
       </c>
       <c r="K24" t="n">
-        <v>1.390299823157506</v>
+        <v>1.905757467101917</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.136198915362837</v>
+        <v>0.1040877461986603</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09763636694153488</v>
+        <v>0.07461694837624766</v>
       </c>
       <c r="F25" t="n">
-        <v>3.53189612560981</v>
+        <v>3.531894413781419</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>434.6410662895514</v>
+        <v>428.0534356319416</v>
       </c>
       <c r="I25" t="n">
-        <v>3191.22266966413</v>
+        <v>4112.42870813021</v>
       </c>
       <c r="J25" t="n">
-        <v>2.53409825265132</v>
+        <v>1.431711165812691</v>
       </c>
       <c r="K25" t="n">
-        <v>1.341706332290278</v>
+        <v>1.823113148403234</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1321583075968141</v>
+        <v>0.1063439970442272</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09507105578471209</v>
+        <v>0.07806374378613323</v>
       </c>
       <c r="F26" t="n">
-        <v>3.563442992928623</v>
+        <v>3.760362259619814</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>435.5455898990688</v>
+        <v>453.1747675640818</v>
       </c>
       <c r="I26" t="n">
-        <v>3295.635346873709</v>
+        <v>4261.404312042284</v>
       </c>
       <c r="J26" t="n">
-        <v>2.476325744826906</v>
+        <v>1.358060297250034</v>
       </c>
       <c r="K26" t="n">
-        <v>1.292607015409274</v>
+        <v>1.766185514056607</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1457563002312957</v>
+        <v>0.1022655178985731</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1107463125358571</v>
+        <v>0.07489556417596854</v>
       </c>
       <c r="F27" t="n">
-        <v>4.163277676623851</v>
+        <v>3.736415447941125</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>508.014426102324</v>
+        <v>456.1675285358292</v>
       </c>
       <c r="I27" t="n">
-        <v>3485.368559000011</v>
+        <v>4460.619159903498</v>
       </c>
       <c r="J27" t="n">
-        <v>2.730080896926595</v>
+        <v>1.330274566819548</v>
       </c>
       <c r="K27" t="n">
-        <v>1.328976523251361</v>
+        <v>1.764244123779868</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1420514467776672</v>
+        <v>0.1003917685701611</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1080058692688445</v>
+        <v>0.07393270293987175</v>
       </c>
       <c r="F28" t="n">
-        <v>4.172390576745403</v>
+        <v>3.794229545855023</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>503.9446283424147</v>
+        <v>459.8722326639115</v>
       </c>
       <c r="I28" t="n">
-        <v>3547.620526041999</v>
+        <v>4580.776284885542</v>
       </c>
       <c r="J28" t="n">
-        <v>2.623691073309471</v>
+        <v>1.28733098465651</v>
       </c>
       <c r="K28" t="n">
-        <v>1.288284343822817</v>
+        <v>1.765818634987249</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1364247552592991</v>
+        <v>0.09962977334173799</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1034638680554557</v>
+        <v>0.07405107372076469</v>
       </c>
       <c r="F29" t="n">
-        <v>4.138989172700144</v>
+        <v>3.89502886456535</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>501.7543464260695</v>
+        <v>472.1142814841938</v>
       </c>
       <c r="I29" t="n">
-        <v>3677.883427185905</v>
+        <v>4738.686696242945</v>
       </c>
       <c r="J29" t="n">
-        <v>2.413167830989561</v>
+        <v>1.285748273164851</v>
       </c>
       <c r="K29" t="n">
-        <v>1.247691113549155</v>
+        <v>1.762539777857683</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1385749954450141</v>
+        <v>0.1011255131322471</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1069049585128454</v>
+        <v>0.07656610092274563</v>
       </c>
       <c r="F30" t="n">
-        <v>4.375586796498414</v>
+        <v>4.117586865255842</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>527.415003579189</v>
+        <v>498.2850940214184</v>
       </c>
       <c r="I30" t="n">
-        <v>3805.989687284276</v>
+        <v>4927.392490654511</v>
       </c>
       <c r="J30" t="n">
-        <v>2.549222284304306</v>
+        <v>1.30872720781584</v>
       </c>
       <c r="K30" t="n">
-        <v>1.222493011579532</v>
+        <v>1.677740095842071</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1340293701835343</v>
+        <v>0.09749689648462864</v>
       </c>
       <c r="E31" t="n">
-        <v>0.103101847690089</v>
+        <v>0.07362115300538596</v>
       </c>
       <c r="F31" t="n">
-        <v>4.333660098766093</v>
+        <v>4.083512480748155</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>520.1773483970901</v>
+        <v>489.6499624408995</v>
       </c>
       <c r="I31" t="n">
-        <v>3881.069855694917</v>
+        <v>5022.210758453196</v>
       </c>
       <c r="J31" t="n">
-        <v>2.413806199372829</v>
+        <v>1.225342499239683</v>
       </c>
       <c r="K31" t="n">
-        <v>1.184717535523545</v>
+        <v>1.566078893637989</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1293003964180958</v>
+        <v>0.09007714231136131</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0992762721566508</v>
+        <v>0.06674578698601175</v>
       </c>
       <c r="F32" t="n">
-        <v>4.306550135889724</v>
+        <v>3.860776241039531</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>518.9017830358459</v>
+        <v>468.413429073235</v>
       </c>
       <c r="I32" t="n">
-        <v>4013.149204569837</v>
+        <v>5200.136428108628</v>
       </c>
       <c r="J32" t="n">
-        <v>2.233092293451372</v>
+        <v>1.161438859432664</v>
       </c>
       <c r="K32" t="n">
-        <v>1.16159442470981</v>
+        <v>1.525093138561408</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1309758957012898</v>
+        <v>0.08660965689214624</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1020084255579993</v>
+        <v>0.06388850407851809</v>
       </c>
       <c r="F33" t="n">
-        <v>4.521482029787382</v>
+        <v>3.811851344100707</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>547.3252115393125</v>
+        <v>462.4034272908759</v>
       </c>
       <c r="I33" t="n">
-        <v>4178.823963056301</v>
+        <v>5338.936140420233</v>
       </c>
       <c r="J33" t="n">
-        <v>2.177278759910908</v>
+        <v>1.142081951706424</v>
       </c>
       <c r="K33" t="n">
-        <v>1.171534160179125</v>
+        <v>1.53629340090809</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1282035112481497</v>
+        <v>0.0849996642237143</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09989843044451807</v>
+        <v>0.06289820683781355</v>
       </c>
       <c r="F34" t="n">
-        <v>4.529346237785738</v>
+        <v>3.84588503552435</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>547.5123161406041</v>
+        <v>470.7085778049638</v>
       </c>
       <c r="I34" t="n">
-        <v>4270.649928462908</v>
+        <v>5537.769850079472</v>
       </c>
       <c r="J34" t="n">
-        <v>2.13242129921538</v>
+        <v>1.12905800419472</v>
       </c>
       <c r="K34" t="n">
-        <v>1.151473599172981</v>
+        <v>1.515326970750297</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1345982491857445</v>
+        <v>0.08529078139906697</v>
       </c>
       <c r="E35" t="n">
-        <v>0.107384357650705</v>
+        <v>0.06391907068409186</v>
       </c>
       <c r="F35" t="n">
-        <v>4.945939062498329</v>
+        <v>3.990826122276869</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>598.6203817281471</v>
+        <v>495.2661283482794</v>
       </c>
       <c r="I35" t="n">
-        <v>4447.460389340251</v>
+        <v>5806.795531992831</v>
       </c>
       <c r="J35" t="n">
-        <v>2.162454452887919</v>
+        <v>1.145735358243517</v>
       </c>
       <c r="K35" t="n">
-        <v>1.12699127796414</v>
+        <v>1.4445035810029</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1344342009580813</v>
+        <v>0.08817803702755017</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1080449997677788</v>
+        <v>0.06745481059635816</v>
       </c>
       <c r="F36" t="n">
-        <v>5.094288379122427</v>
+        <v>4.255034191723494</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>614.9969775852575</v>
+        <v>530.8295601629377</v>
       </c>
       <c r="I36" t="n">
-        <v>4574.706236971821</v>
+        <v>6019.974792556182</v>
       </c>
       <c r="J36" t="n">
-        <v>2.221055835535509</v>
+        <v>1.216869314021533</v>
       </c>
       <c r="K36" t="n">
-        <v>1.102539737635598</v>
+        <v>1.398275645257854</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1379464757772148</v>
+        <v>0.09264532591648082</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1122901208896321</v>
+        <v>0.07257110746330564</v>
       </c>
       <c r="F37" t="n">
-        <v>5.376698146780696</v>
+        <v>4.61513986871189</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>651.8955930844807</v>
+        <v>576.2274748651469</v>
       </c>
       <c r="I37" t="n">
-        <v>4725.714009086392</v>
+        <v>6219.714477388879</v>
       </c>
       <c r="J37" t="n">
-        <v>2.40650273850035</v>
+        <v>1.243713345453118</v>
       </c>
       <c r="K37" t="n">
-        <v>1.093745481262665</v>
+        <v>1.343172852876731</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1291953771568483</v>
+        <v>0.09657106609574953</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1040276134908612</v>
+        <v>0.07710061493401998</v>
       </c>
       <c r="F38" t="n">
-        <v>5.133367385019165</v>
+        <v>4.959878191501097</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>630.3950869957489</v>
+        <v>623.4876702883221</v>
       </c>
       <c r="I38" t="n">
-        <v>4879.393526832037</v>
+        <v>6456.257505432719</v>
       </c>
       <c r="J38" t="n">
-        <v>2.262627041043107</v>
+        <v>1.362041503548485</v>
       </c>
       <c r="K38" t="n">
-        <v>1.075456417574971</v>
+        <v>1.316498553918304</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.121464893467048</v>
+        <v>0.09883694650356667</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09678694103634722</v>
+        <v>0.07990494958137273</v>
       </c>
       <c r="F39" t="n">
-        <v>4.922000470182371</v>
+        <v>5.220629757640629</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>607.1900035559963</v>
+        <v>652.8549803920434</v>
       </c>
       <c r="I39" t="n">
-        <v>4998.892982363828</v>
+        <v>6605.373835263965</v>
       </c>
       <c r="J39" t="n">
-        <v>2.075982907154741</v>
+        <v>1.363406394794973</v>
       </c>
       <c r="K39" t="n">
-        <v>1.069226679063282</v>
+        <v>1.309612094759369</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1139363680442187</v>
+        <v>0.09893622620886414</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08959396057290614</v>
+        <v>0.08054716960088171</v>
       </c>
       <c r="F40" t="n">
-        <v>4.680571064242177</v>
+        <v>5.380168668680788</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>589.4154356199374</v>
+        <v>668.7688167911447</v>
       </c>
       <c r="I40" t="n">
-        <v>5173.198389044535</v>
+        <v>6759.594967563324</v>
       </c>
       <c r="J40" t="n">
-        <v>1.910400939725669</v>
+        <v>1.290541915697616</v>
       </c>
       <c r="K40" t="n">
-        <v>1.061724624311823</v>
+        <v>1.251631223588467</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1096830736851434</v>
+        <v>0.1007119159571339</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08587780827565517</v>
+        <v>0.08279781069731584</v>
       </c>
       <c r="F41" t="n">
-        <v>4.607513161412881</v>
+        <v>5.621933917237505</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>579.1157120828823</v>
+        <v>692.0095568149876</v>
       </c>
       <c r="I41" t="n">
-        <v>5279.900468009256</v>
+        <v>6871.17855159789</v>
       </c>
       <c r="J41" t="n">
-        <v>1.848383125923893</v>
+        <v>1.264016182041214</v>
       </c>
       <c r="K41" t="n">
-        <v>1.055373750875181</v>
+        <v>1.199891550092927</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1066404462175381</v>
+        <v>0.1030525386987009</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08337587450445305</v>
+        <v>0.08560219898466792</v>
       </c>
       <c r="F42" t="n">
-        <v>4.583812998266335</v>
+        <v>5.905474643329093</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>569.6244447564569</v>
+        <v>721.381553383932</v>
       </c>
       <c r="I42" t="n">
-        <v>5341.542209927255</v>
+        <v>7000.133742391987</v>
       </c>
       <c r="J42" t="n">
-        <v>1.813147073168272</v>
+        <v>1.220269109429514</v>
       </c>
       <c r="K42" t="n">
-        <v>1.03992929603375</v>
+        <v>1.169630835279525</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1081169200077596</v>
+        <v>0.1055053950955397</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08536480062020246</v>
+        <v>0.08849979424184273</v>
       </c>
       <c r="F43" t="n">
-        <v>4.751949397157583</v>
+        <v>6.204155678074918</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>586.2306873424116</v>
+        <v>764.1295026703158</v>
       </c>
       <c r="I43" t="n">
-        <v>5422.191894666788</v>
+        <v>7242.563301889571</v>
       </c>
       <c r="J43" t="n">
-        <v>1.828783662473239</v>
+        <v>1.248470023017887</v>
       </c>
       <c r="K43" t="n">
-        <v>1.034862878507022</v>
+        <v>1.153565813311923</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1043571600106309</v>
+        <v>0.1080609039580751</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08207748737407938</v>
+        <v>0.0914821103513479</v>
       </c>
       <c r="F44" t="n">
-        <v>4.683962898064542</v>
+        <v>6.518019737831039</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>577.0079984698026</v>
+        <v>796.8231448710821</v>
       </c>
       <c r="I44" t="n">
-        <v>5529.165400927186</v>
+        <v>7373.833788955063</v>
       </c>
       <c r="J44" t="n">
-        <v>1.749791547851857</v>
+        <v>1.347967430149884</v>
       </c>
       <c r="K44" t="n">
-        <v>1.046335461079806</v>
+        <v>1.098145616636176</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09601556918796182</v>
+        <v>0.1181322542476465</v>
       </c>
       <c r="E45" t="n">
-        <v>0.07407419950805805</v>
+        <v>0.1021563892883647</v>
       </c>
       <c r="F45" t="n">
-        <v>4.376006174122426</v>
+        <v>7.394419929608456</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>544.0133733480424</v>
+        <v>901.7933026164155</v>
       </c>
       <c r="I45" t="n">
-        <v>5665.887084240181</v>
+        <v>7633.760215274838</v>
       </c>
       <c r="J45" t="n">
-        <v>1.547169398511505</v>
+        <v>1.567926860869972</v>
       </c>
       <c r="K45" t="n">
-        <v>1.03090999921904</v>
+        <v>1.071799870435109</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09633975296739716</v>
+        <v>0.1232798328362171</v>
       </c>
       <c r="E46" t="n">
-        <v>0.07482403279995431</v>
+        <v>0.1077351490212564</v>
       </c>
       <c r="F46" t="n">
-        <v>4.477644820514824</v>
+        <v>7.930674840588827</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>555.28812656123</v>
+        <v>964.881211384007</v>
       </c>
       <c r="I46" t="n">
-        <v>5763.852505923987</v>
+        <v>7826.756324904301</v>
       </c>
       <c r="J46" t="n">
-        <v>1.524658062332032</v>
+        <v>1.645847858602487</v>
       </c>
       <c r="K46" t="n">
-        <v>1.030838906046814</v>
+        <v>1.03751635647788</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09655837130762868</v>
+        <v>0.1245071683981215</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0755481008729223</v>
+        <v>0.1093076400716999</v>
       </c>
       <c r="F47" t="n">
-        <v>4.595770035788138</v>
+        <v>8.191515271015968</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>568.2926754050744</v>
+        <v>1000.900847325988</v>
       </c>
       <c r="I47" t="n">
-        <v>5885.483233706697</v>
+        <v>8038.901375746723</v>
       </c>
       <c r="J47" t="n">
-        <v>1.514057487768083</v>
+        <v>1.698056131958137</v>
       </c>
       <c r="K47" t="n">
-        <v>1.019499280334781</v>
+        <v>1.024696375436378</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09412845847468054</v>
+        <v>0.1279378612699769</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07354046889455967</v>
+        <v>0.113106872516065</v>
       </c>
       <c r="F48" t="n">
-        <v>4.57200826279648</v>
+        <v>8.626387855376858</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>564.2783047438895</v>
+        <v>1041.733259007402</v>
       </c>
       <c r="I48" t="n">
-        <v>5994.768361108068</v>
+        <v>8142.493931558833</v>
       </c>
       <c r="J48" t="n">
-        <v>1.42949949753762</v>
+        <v>1.811530287591399</v>
       </c>
       <c r="K48" t="n">
-        <v>1.008443193196477</v>
+        <v>1.011367841941263</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.09581462343086448</v>
+        <v>0.1324739318838206</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07563191413244619</v>
+        <v>0.1180151640818844</v>
       </c>
       <c r="F49" t="n">
-        <v>4.747361814222526</v>
+        <v>9.162186826603561</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>580.3839552400905</v>
+        <v>1099.30803902438</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.363004289939</v>
+        <v>8298.297056574651</v>
       </c>
       <c r="J49" t="n">
-        <v>1.468911117005158</v>
+        <v>1.963005611137663</v>
       </c>
       <c r="K49" t="n">
-        <v>1.004401483699101</v>
+        <v>1.000680674263687</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3902551118339467</v>
+        <v>0.4568956108419263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05150795174169498</v>
+        <v>0.1551709501985519</v>
       </c>
       <c r="F2" t="n">
-        <v>1.152054268817096</v>
+        <v>1.514279972567298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.347</v>
+        <v>0.067</v>
       </c>
       <c r="H2" t="n">
-        <v>122.0619721893547</v>
+        <v>149.9410445521718</v>
       </c>
       <c r="I2" t="n">
-        <v>312.7748195680061</v>
+        <v>328.1735280316524</v>
       </c>
       <c r="J2" t="n">
-        <v>5.084730382237121</v>
+        <v>5.541323242609988</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05801854132884</v>
+        <v>12.46116992076206</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.285841571444759</v>
+        <v>0.4170494110931831</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04778876192634551</v>
+        <v>0.2227325481242441</v>
       </c>
       <c r="F3" t="n">
-        <v>1.200748573490996</v>
+        <v>2.146233758208866</v>
       </c>
       <c r="G3" t="n">
-        <v>0.269</v>
+        <v>0.002</v>
       </c>
       <c r="H3" t="n">
-        <v>128.3256227886046</v>
+        <v>177.7070216532159</v>
       </c>
       <c r="I3" t="n">
-        <v>448.9396771085287</v>
+        <v>426.1054372128343</v>
       </c>
       <c r="J3" t="n">
-        <v>4.061832316873462</v>
+        <v>4.000647927642576</v>
       </c>
       <c r="K3" t="n">
-        <v>3.111508302276199</v>
+        <v>7.011834544271273</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2879157375982248</v>
+        <v>0.2902449085556826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.118371865597802</v>
+        <v>0.1212556010689404</v>
       </c>
       <c r="F4" t="n">
-        <v>1.698178378263692</v>
+        <v>1.717534161612285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="H4" t="n">
-        <v>156.9833392121839</v>
+        <v>194.7248360067672</v>
       </c>
       <c r="I4" t="n">
-        <v>545.2405642071851</v>
+        <v>670.8983698482685</v>
       </c>
       <c r="J4" t="n">
-        <v>3.149159078476893</v>
+        <v>2.788162902254624</v>
       </c>
       <c r="K4" t="n">
-        <v>3.198313803284687</v>
+        <v>5.289933109321636</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2791386690823043</v>
+        <v>0.2271748192507106</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1504134314184301</v>
+        <v>0.08917032268833747</v>
       </c>
       <c r="F5" t="n">
-        <v>2.168484394732194</v>
+        <v>1.646140704901131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="H5" t="n">
-        <v>215.2169192747143</v>
+        <v>172.1262163719695</v>
       </c>
       <c r="I5" t="n">
-        <v>771.0036018379717</v>
+        <v>757.681757774442</v>
       </c>
       <c r="J5" t="n">
-        <v>3.442725468488121</v>
+        <v>2.296283018428897</v>
       </c>
       <c r="K5" t="n">
-        <v>3.570574357503849</v>
+        <v>4.585349916975876</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2215351826320979</v>
+        <v>0.2397340870099577</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1070550624309359</v>
+        <v>0.127930276276128</v>
       </c>
       <c r="F6" t="n">
-        <v>1.935141072902621</v>
+        <v>2.144238961413313</v>
       </c>
       <c r="G6" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>206.7618655204346</v>
+        <v>222.6792254625121</v>
       </c>
       <c r="I6" t="n">
-        <v>933.3139010420878</v>
+        <v>928.8592550180933</v>
       </c>
       <c r="J6" t="n">
-        <v>2.616430655873559</v>
+        <v>2.583265797939834</v>
       </c>
       <c r="K6" t="n">
-        <v>2.839884339308284</v>
+        <v>4.207288678502959</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1442630508228531</v>
+        <v>0.1874863816405586</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0372959321757097</v>
+        <v>0.0859221793456284</v>
       </c>
       <c r="F7" t="n">
-        <v>1.348667260064649</v>
+        <v>1.845988816966441</v>
       </c>
       <c r="G7" t="n">
-        <v>0.138</v>
+        <v>0.007</v>
       </c>
       <c r="H7" t="n">
-        <v>178.1550630549485</v>
+        <v>188.8096711457405</v>
       </c>
       <c r="I7" t="n">
-        <v>1234.932035880156</v>
+        <v>1007.058056663117</v>
       </c>
       <c r="J7" t="n">
-        <v>2.239931281329944</v>
+        <v>1.887664948979732</v>
       </c>
       <c r="K7" t="n">
-        <v>1.989662537849751</v>
+        <v>4.582571544998873</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1238569898220696</v>
+        <v>0.1401719317630846</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02862405393316414</v>
+        <v>0.04671235912863714</v>
       </c>
       <c r="F8" t="n">
-        <v>1.300568849064526</v>
+        <v>1.499813532331733</v>
       </c>
       <c r="G8" t="n">
-        <v>0.196</v>
+        <v>0.045</v>
       </c>
       <c r="H8" t="n">
-        <v>169.2648005522443</v>
+        <v>165.9583196885453</v>
       </c>
       <c r="I8" t="n">
-        <v>1366.614841805914</v>
+        <v>1183.962563696734</v>
       </c>
       <c r="J8" t="n">
-        <v>2.075408200513311</v>
+        <v>1.389865096415476</v>
       </c>
       <c r="K8" t="n">
-        <v>1.588741709231285</v>
+        <v>4.751013803875194</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1331300205454433</v>
+        <v>0.1387270227278616</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04977713790558203</v>
+        <v>0.05591231337477132</v>
       </c>
       <c r="F9" t="n">
-        <v>1.597185560104162</v>
+        <v>1.675149545431388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05</v>
+        <v>0.012</v>
       </c>
       <c r="H9" t="n">
-        <v>207.6005435731717</v>
+        <v>182.5025798754094</v>
       </c>
       <c r="I9" t="n">
-        <v>1559.381893900544</v>
+        <v>1315.551766964836</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4791546764683</v>
+        <v>1.178254542241128</v>
       </c>
       <c r="K9" t="n">
-        <v>1.492846890595561</v>
+        <v>4.043009245576484</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1201749142244229</v>
+        <v>0.1471492235337445</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0456134662773402</v>
+        <v>0.07487373400270592</v>
       </c>
       <c r="F10" t="n">
-        <v>1.611756712526728</v>
+        <v>2.035949178463211</v>
       </c>
       <c r="G10" t="n">
-        <v>0.063</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>211.6889954908883</v>
+        <v>213.8047511200689</v>
       </c>
       <c r="I10" t="n">
-        <v>1761.507356648207</v>
+        <v>1452.979132241488</v>
       </c>
       <c r="J10" t="n">
-        <v>2.128364917438009</v>
+        <v>1.458209193359361</v>
       </c>
       <c r="K10" t="n">
-        <v>1.305323814555845</v>
+        <v>3.863675808228423</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1093878897908734</v>
+        <v>0.1423943748300761</v>
       </c>
       <c r="E11" t="n">
-        <v>0.040879265928633</v>
+        <v>0.07642471135546658</v>
       </c>
       <c r="F11" t="n">
-        <v>1.596702482461688</v>
+        <v>2.158482662032692</v>
       </c>
       <c r="G11" t="n">
-        <v>0.051</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>205.6739559649264</v>
+        <v>228.8886081717682</v>
       </c>
       <c r="I11" t="n">
-        <v>1880.226013666884</v>
+        <v>1607.4273189858</v>
       </c>
       <c r="J11" t="n">
-        <v>2.044150312386404</v>
+        <v>1.700732370901531</v>
       </c>
       <c r="K11" t="n">
-        <v>1.531242495564548</v>
+        <v>3.156308824963756</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1126380981254764</v>
+        <v>0.1367125770048068</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05014782334558043</v>
+        <v>0.07591768806148336</v>
       </c>
       <c r="F12" t="n">
-        <v>1.802490043806202</v>
+        <v>2.248751159530173</v>
       </c>
       <c r="G12" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="n">
-        <v>227.7034650697627</v>
+        <v>238.4258602514503</v>
       </c>
       <c r="I12" t="n">
-        <v>2021.549270266496</v>
+        <v>1743.993606696971</v>
       </c>
       <c r="J12" t="n">
-        <v>1.82863220919355</v>
+        <v>1.702803575507933</v>
       </c>
       <c r="K12" t="n">
-        <v>1.477087136409038</v>
+        <v>3.373937042054666</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1105716531982852</v>
+        <v>0.1443422530587507</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05281656574362847</v>
+        <v>0.08878006169892938</v>
       </c>
       <c r="F13" t="n">
-        <v>1.914492005316316</v>
+        <v>2.597850256192896</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>248.6133105126329</v>
+        <v>279.8031359574275</v>
       </c>
       <c r="I13" t="n">
-        <v>2248.436225031395</v>
+        <v>1938.470060069943</v>
       </c>
       <c r="J13" t="n">
-        <v>1.899022449669885</v>
+        <v>2.108680480412622</v>
       </c>
       <c r="K13" t="n">
-        <v>1.602580235453608</v>
+        <v>3.487246342839963</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1001002216549968</v>
+        <v>0.144032215186562</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04588939163421335</v>
+        <v>0.09246789080021034</v>
       </c>
       <c r="F14" t="n">
-        <v>1.846498598464927</v>
+        <v>2.793253221110469</v>
       </c>
       <c r="G14" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>241.6826553952741</v>
+        <v>299.9452086194847</v>
       </c>
       <c r="I14" t="n">
-        <v>2414.406795503932</v>
+        <v>2082.486950790639</v>
       </c>
       <c r="J14" t="n">
-        <v>1.662474314128731</v>
+        <v>2.100564467500354</v>
       </c>
       <c r="K14" t="n">
-        <v>1.715434961372016</v>
+        <v>3.912257189516079</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1111902380761392</v>
+        <v>0.1316525936917952</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06181191796925811</v>
+        <v>0.08341107111911716</v>
       </c>
       <c r="F15" t="n">
-        <v>2.251802771650878</v>
+        <v>2.729030649757263</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>287.2023491648429</v>
+        <v>306.0056227811122</v>
       </c>
       <c r="I15" t="n">
-        <v>2582.981690966221</v>
+        <v>2324.341771021127</v>
       </c>
       <c r="J15" t="n">
-        <v>1.745200153297574</v>
+        <v>1.772216332055066</v>
       </c>
       <c r="K15" t="n">
-        <v>1.659856070261798</v>
+        <v>2.836080432327783</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1060478296695005</v>
+        <v>0.1345266159392734</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05948782079812043</v>
+        <v>0.08944987718611064</v>
       </c>
       <c r="F16" t="n">
-        <v>2.277659137962208</v>
+        <v>2.984391055349678</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>289.4739106346469</v>
+        <v>342.6629712287069</v>
       </c>
       <c r="I16" t="n">
-        <v>2729.654265785507</v>
+        <v>2547.176027853018</v>
       </c>
       <c r="J16" t="n">
-        <v>1.60965813271052</v>
+        <v>1.639729679564443</v>
       </c>
       <c r="K16" t="n">
-        <v>1.858737118002542</v>
+        <v>2.85477122007719</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1025326218239311</v>
+        <v>0.1421515940071339</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05853912289373153</v>
+        <v>0.1001002015565031</v>
       </c>
       <c r="F17" t="n">
-        <v>2.330631214093938</v>
+        <v>3.38042537292964</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>300.1370712832941</v>
+        <v>384.6198582107536</v>
       </c>
       <c r="I17" t="n">
-        <v>2927.234922351728</v>
+        <v>2705.70204222579</v>
       </c>
       <c r="J17" t="n">
-        <v>1.613642578379915</v>
+        <v>1.895487375868248</v>
       </c>
       <c r="K17" t="n">
-        <v>1.859498968539945</v>
+        <v>3.159482888788578</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.10496574440099</v>
+        <v>0.140752636302471</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06352897330844332</v>
+        <v>0.1009726657609188</v>
       </c>
       <c r="F18" t="n">
-        <v>2.533154529983883</v>
+        <v>3.538279048131709</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>325.0013862782683</v>
+        <v>412.1046143862952</v>
       </c>
       <c r="I18" t="n">
-        <v>3096.261433984581</v>
+        <v>2927.864267499055</v>
       </c>
       <c r="J18" t="n">
-        <v>1.736267353296915</v>
+        <v>1.773383468449164</v>
       </c>
       <c r="K18" t="n">
-        <v>1.905528612781861</v>
+        <v>3.303445801616741</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09580553594699841</v>
+        <v>0.1467427387363908</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05614788401484927</v>
+        <v>0.1093191746458817</v>
       </c>
       <c r="F19" t="n">
-        <v>2.415814635493633</v>
+        <v>3.921132107607184</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>314.8455803023907</v>
+        <v>456.8002478965944</v>
       </c>
       <c r="I19" t="n">
-        <v>3286.298408440298</v>
+        <v>3112.932550054092</v>
       </c>
       <c r="J19" t="n">
-        <v>1.520807982666343</v>
+        <v>1.827622238706009</v>
       </c>
       <c r="K19" t="n">
-        <v>1.98413360630721</v>
+        <v>3.265267152349054</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09822262083449904</v>
+        <v>0.1361282142176755</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06095909276980882</v>
+        <v>0.1004310329870008</v>
       </c>
       <c r="F20" t="n">
-        <v>2.635891605968788</v>
+        <v>3.813416340579312</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>340.5774747173907</v>
+        <v>459.861822926235</v>
       </c>
       <c r="I20" t="n">
-        <v>3467.403657363708</v>
+        <v>3378.152174911323</v>
       </c>
       <c r="J20" t="n">
-        <v>1.478859384748739</v>
+        <v>1.740342118817471</v>
       </c>
       <c r="K20" t="n">
-        <v>1.843060346625855</v>
+        <v>3.181969035660362</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1010914950295502</v>
+        <v>0.1357846410780389</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06570139640866646</v>
+        <v>0.1017604143488279</v>
       </c>
       <c r="F21" t="n">
-        <v>2.85649091042362</v>
+        <v>3.990822250236851</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>361.3446443966353</v>
+        <v>480.6059195129899</v>
       </c>
       <c r="I21" t="n">
-        <v>3574.431699630222</v>
+        <v>3539.471885018082</v>
       </c>
       <c r="J21" t="n">
-        <v>1.460803219529729</v>
+        <v>1.750855853892436</v>
       </c>
       <c r="K21" t="n">
-        <v>1.90676609152101</v>
+        <v>3.160622833325821</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1008193867733274</v>
+        <v>0.1395428521637513</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0670156043211968</v>
+        <v>0.1071948390872005</v>
       </c>
       <c r="F22" t="n">
-        <v>2.98248833295793</v>
+        <v>4.313799794550807</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>374.9606772598279</v>
+        <v>528.9491345408342</v>
       </c>
       <c r="I22" t="n">
-        <v>3719.132691243733</v>
+        <v>3790.585661242763</v>
       </c>
       <c r="J22" t="n">
-        <v>1.45164685760238</v>
+        <v>1.920298476856783</v>
       </c>
       <c r="K22" t="n">
-        <v>1.976275763327762</v>
+        <v>2.888879468025722</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0997576773725929</v>
+        <v>0.1404635003364286</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06737486001189474</v>
+        <v>0.1095449212118396</v>
       </c>
       <c r="F23" t="n">
-        <v>3.080574375646059</v>
+        <v>4.543012787567617</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>380.88809235367</v>
+        <v>550.8369452410997</v>
       </c>
       <c r="I23" t="n">
-        <v>3818.133124040776</v>
+        <v>3921.566413493702</v>
       </c>
       <c r="J23" t="n">
-        <v>1.354262012013912</v>
+        <v>1.86049454716113</v>
       </c>
       <c r="K23" t="n">
-        <v>1.922732074176519</v>
+        <v>2.917873413618331</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1044499755888136</v>
+        <v>0.1469256048726847</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07356894026428995</v>
+        <v>0.1175092464200187</v>
       </c>
       <c r="F24" t="n">
-        <v>3.38233399531998</v>
+        <v>4.994690458001564</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>411.0598811792544</v>
+        <v>601.5883773000344</v>
       </c>
       <c r="I24" t="n">
-        <v>3935.471299653211</v>
+        <v>4094.510128587376</v>
       </c>
       <c r="J24" t="n">
-        <v>1.438157829846628</v>
+        <v>1.862705256200476</v>
       </c>
       <c r="K24" t="n">
-        <v>1.905757467101917</v>
+        <v>3.051553718225375</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1040877461986603</v>
+        <v>0.1465668783455728</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07461694837624766</v>
+        <v>0.118493420396414</v>
       </c>
       <c r="F25" t="n">
-        <v>3.531894413781419</v>
+        <v>5.220834519602336</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>428.0534356319416</v>
+        <v>632.1756209152793</v>
       </c>
       <c r="I25" t="n">
-        <v>4112.42870813021</v>
+        <v>4313.222933115535</v>
       </c>
       <c r="J25" t="n">
-        <v>1.431711165812691</v>
+        <v>1.875435958370279</v>
       </c>
       <c r="K25" t="n">
-        <v>1.823113148403234</v>
+        <v>3.023711135358233</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1063439970442272</v>
+        <v>0.1649177796890144</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07806374378613323</v>
+        <v>0.1384911271475276</v>
       </c>
       <c r="F26" t="n">
-        <v>3.760362259619814</v>
+        <v>6.240585311745858</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>453.1747675640818</v>
+        <v>747.6395368812815</v>
       </c>
       <c r="I26" t="n">
-        <v>4261.404312042284</v>
+        <v>4533.407727724118</v>
       </c>
       <c r="J26" t="n">
-        <v>1.358060297250034</v>
+        <v>2.178558498028405</v>
       </c>
       <c r="K26" t="n">
-        <v>1.766185514056607</v>
+        <v>2.844331280723826</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1022655178985731</v>
+        <v>0.1554583011736912</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07489556417596854</v>
+        <v>0.1297100786484988</v>
       </c>
       <c r="F27" t="n">
-        <v>3.736415447941125</v>
+        <v>6.037632346139198</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>456.1675285358292</v>
+        <v>722.7078226902349</v>
       </c>
       <c r="I27" t="n">
-        <v>4460.619159903498</v>
+        <v>4648.8853746238</v>
       </c>
       <c r="J27" t="n">
-        <v>1.330274566819548</v>
+        <v>1.909304938902195</v>
       </c>
       <c r="K27" t="n">
-        <v>1.764244123779868</v>
+        <v>2.711990084296679</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1003917685701611</v>
+        <v>0.1542641559362876</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07393270293987175</v>
+        <v>0.129389572287355</v>
       </c>
       <c r="F28" t="n">
-        <v>3.794229545855023</v>
+        <v>6.201677910010228</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>459.8722326639115</v>
+        <v>749.495558866088</v>
       </c>
       <c r="I28" t="n">
-        <v>4580.776284885542</v>
+        <v>4858.520466514825</v>
       </c>
       <c r="J28" t="n">
-        <v>1.28733098465651</v>
+        <v>1.981370042644517</v>
       </c>
       <c r="K28" t="n">
-        <v>1.765818634987249</v>
+        <v>2.779660679728865</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09962977334173799</v>
+        <v>0.1430687404626597</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07405107372076469</v>
+        <v>0.1187241024076217</v>
       </c>
       <c r="F29" t="n">
-        <v>3.89502886456535</v>
+        <v>5.876807046348834</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>472.1142814841938</v>
+        <v>719.1757619894113</v>
       </c>
       <c r="I29" t="n">
-        <v>4738.686696242945</v>
+        <v>5026.784744618011</v>
       </c>
       <c r="J29" t="n">
-        <v>1.285748273164851</v>
+        <v>1.909859768693513</v>
       </c>
       <c r="K29" t="n">
-        <v>1.762539777857683</v>
+        <v>2.548172138601938</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1011255131322471</v>
+        <v>0.1393051743368366</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07656610092274563</v>
+        <v>0.115788922269537</v>
       </c>
       <c r="F30" t="n">
-        <v>4.117586865255842</v>
+        <v>5.923783004969018</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>498.2850940214184</v>
+        <v>721.5992752911889</v>
       </c>
       <c r="I30" t="n">
-        <v>4927.392490654511</v>
+        <v>5179.989032901098</v>
       </c>
       <c r="J30" t="n">
-        <v>1.30872720781584</v>
+        <v>1.810956930999748</v>
       </c>
       <c r="K30" t="n">
-        <v>1.677740095842071</v>
+        <v>2.360826617496193</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09749689648462864</v>
+        <v>0.1351834293713831</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07362115300538596</v>
+        <v>0.1123046841166578</v>
       </c>
       <c r="F31" t="n">
-        <v>4.083512480748155</v>
+        <v>5.908690702496575</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>489.6499624408995</v>
+        <v>731.9695596753853</v>
       </c>
       <c r="I31" t="n">
-        <v>5022.210758453196</v>
+        <v>5414.639672030213</v>
       </c>
       <c r="J31" t="n">
-        <v>1.225342499239683</v>
+        <v>1.770875079991178</v>
       </c>
       <c r="K31" t="n">
-        <v>1.566078893637989</v>
+        <v>2.252142234352105</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09007714231136131</v>
+        <v>0.1416938852545514</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06674578698601175</v>
+        <v>0.1196860361585144</v>
       </c>
       <c r="F32" t="n">
-        <v>3.860776241039531</v>
+        <v>6.438334097813567</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>468.413429073235</v>
+        <v>792.647550860581</v>
       </c>
       <c r="I32" t="n">
-        <v>5200.136428108628</v>
+        <v>5594.084384351511</v>
       </c>
       <c r="J32" t="n">
-        <v>1.161438859432664</v>
+        <v>1.963497747395103</v>
       </c>
       <c r="K32" t="n">
-        <v>1.525093138561408</v>
+        <v>2.39393545332165</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08660965689214624</v>
+        <v>0.1358037103937778</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06388850407851809</v>
+        <v>0.1143062902543195</v>
       </c>
       <c r="F33" t="n">
-        <v>3.811851344100707</v>
+        <v>6.317209670406527</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>462.4034272908759</v>
+        <v>780.3362712545747</v>
       </c>
       <c r="I33" t="n">
-        <v>5338.936140420233</v>
+        <v>5746.060022895575</v>
       </c>
       <c r="J33" t="n">
-        <v>1.142081951706424</v>
+        <v>1.957020397329691</v>
       </c>
       <c r="K33" t="n">
-        <v>1.53629340090809</v>
+        <v>2.360693946796013</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0849996642237143</v>
+        <v>0.1273478126033915</v>
       </c>
       <c r="E34" t="n">
-        <v>0.06289820683781355</v>
+        <v>0.1062692573522656</v>
       </c>
       <c r="F34" t="n">
-        <v>3.84588503552435</v>
+        <v>6.04158164951034</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>470.7085778049638</v>
+        <v>745.0154587659105</v>
       </c>
       <c r="I34" t="n">
-        <v>5537.769850079472</v>
+        <v>5850.241504235068</v>
       </c>
       <c r="J34" t="n">
-        <v>1.12905800419472</v>
+        <v>1.912301999197503</v>
       </c>
       <c r="K34" t="n">
-        <v>1.515326970750297</v>
+        <v>2.318350796349493</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08529078139906697</v>
+        <v>0.116755868986938</v>
       </c>
       <c r="E35" t="n">
-        <v>0.06391907068409186</v>
+        <v>0.09611932386981037</v>
       </c>
       <c r="F35" t="n">
-        <v>3.990826122276869</v>
+        <v>5.657723631754362</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>495.2661283482794</v>
+        <v>709.8961411933285</v>
       </c>
       <c r="I35" t="n">
-        <v>5806.795531992831</v>
+        <v>6080.175218196079</v>
       </c>
       <c r="J35" t="n">
-        <v>1.145735358243517</v>
+        <v>1.863741169323482</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4445035810029</v>
+        <v>1.849969808708314</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08817803702755017</v>
+        <v>0.118278785676086</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06745481059635816</v>
+        <v>0.09823966716872434</v>
       </c>
       <c r="F36" t="n">
-        <v>4.255034191723494</v>
+        <v>5.902394640394709</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>530.8295601629377</v>
+        <v>740.3644989505985</v>
       </c>
       <c r="I36" t="n">
-        <v>6019.974792556182</v>
+        <v>6259.486810915813</v>
       </c>
       <c r="J36" t="n">
-        <v>1.216869314021533</v>
+        <v>1.869167830166676</v>
       </c>
       <c r="K36" t="n">
-        <v>1.398275645257854</v>
+        <v>1.816204572518471</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.09264532591648082</v>
+        <v>0.1159985086777062</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07257110746330564</v>
+        <v>0.09644095355995641</v>
       </c>
       <c r="F37" t="n">
-        <v>4.61513986871189</v>
+        <v>5.93113546040473</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>576.2274748651469</v>
+        <v>737.2765038732701</v>
       </c>
       <c r="I37" t="n">
-        <v>6219.714477388879</v>
+        <v>6355.913643008478</v>
       </c>
       <c r="J37" t="n">
-        <v>1.243713345453118</v>
+        <v>1.801341760931339</v>
       </c>
       <c r="K37" t="n">
-        <v>1.343172852876731</v>
+        <v>1.738818317349545</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09657106609574953</v>
+        <v>0.1163725588706571</v>
       </c>
       <c r="E38" t="n">
-        <v>0.07710061493401998</v>
+        <v>0.09732886401873164</v>
       </c>
       <c r="F38" t="n">
-        <v>4.959878191501097</v>
+        <v>6.110818293168081</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>623.4876702883221</v>
+        <v>755.7552091672992</v>
       </c>
       <c r="I38" t="n">
-        <v>6456.257505432719</v>
+        <v>6494.273362221819</v>
       </c>
       <c r="J38" t="n">
-        <v>1.362041503548485</v>
+        <v>1.744576409652329</v>
       </c>
       <c r="K38" t="n">
-        <v>1.316498553918304</v>
+        <v>1.723917414263868</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09883694650356667</v>
+        <v>0.1206807630609717</v>
       </c>
       <c r="E39" t="n">
-        <v>0.07990494958137273</v>
+        <v>0.102207669847967</v>
       </c>
       <c r="F39" t="n">
-        <v>5.220629757640629</v>
+        <v>6.532785910267272</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>652.8549803920434</v>
+        <v>803.3780986901667</v>
       </c>
       <c r="I39" t="n">
-        <v>6605.373835263965</v>
+        <v>6657.051864051231</v>
       </c>
       <c r="J39" t="n">
-        <v>1.363406394794973</v>
+        <v>1.887580859119566</v>
       </c>
       <c r="K39" t="n">
-        <v>1.309612094759369</v>
+        <v>1.730369424202916</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09893622620886414</v>
+        <v>0.1263382023600837</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08054716960088171</v>
+        <v>0.1085083697551875</v>
       </c>
       <c r="F40" t="n">
-        <v>5.380168668680788</v>
+        <v>7.085776134846605</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>668.7688167911447</v>
+        <v>861.5157623006871</v>
       </c>
       <c r="I40" t="n">
-        <v>6759.594967563324</v>
+        <v>6819.12316470383</v>
       </c>
       <c r="J40" t="n">
-        <v>1.290541915697616</v>
+        <v>1.890005527602664</v>
       </c>
       <c r="K40" t="n">
-        <v>1.251631223588467</v>
+        <v>1.661132486860555</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1007119159571339</v>
+        <v>0.12678207255688</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08279781069731584</v>
+        <v>0.1093872931257421</v>
       </c>
       <c r="F41" t="n">
-        <v>5.621933917237505</v>
+        <v>7.288512801141435</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>692.0095568149876</v>
+        <v>888.4594587027786</v>
       </c>
       <c r="I41" t="n">
-        <v>6871.17855159789</v>
+        <v>7007.768849213101</v>
       </c>
       <c r="J41" t="n">
-        <v>1.264016182041214</v>
+        <v>1.928864310891267</v>
       </c>
       <c r="K41" t="n">
-        <v>1.199891550092927</v>
+        <v>1.66338143056325</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1030525386987009</v>
+        <v>0.1264517653431163</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08560219898466792</v>
+        <v>0.1094566635015427</v>
       </c>
       <c r="F42" t="n">
-        <v>5.905474643329093</v>
+        <v>7.440482941607835</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>721.381553383932</v>
+        <v>899.8073765770368</v>
       </c>
       <c r="I42" t="n">
-        <v>7000.133742391987</v>
+        <v>7115.815063043876</v>
       </c>
       <c r="J42" t="n">
-        <v>1.220269109429514</v>
+        <v>1.963700829334758</v>
       </c>
       <c r="K42" t="n">
-        <v>1.169630835279525</v>
+        <v>1.716434460286817</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1055053950955397</v>
+        <v>0.1252185586764149</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08849979424184273</v>
+        <v>0.1085877327957384</v>
       </c>
       <c r="F43" t="n">
-        <v>6.204155678074918</v>
+        <v>7.529304892904165</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>764.1295026703158</v>
+        <v>906.4957108359711</v>
       </c>
       <c r="I43" t="n">
-        <v>7242.563301889571</v>
+        <v>7239.307978128889</v>
       </c>
       <c r="J43" t="n">
-        <v>1.248470023017887</v>
+        <v>1.90230397413258</v>
       </c>
       <c r="K43" t="n">
-        <v>1.153565813311923</v>
+        <v>1.744999889776064</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1080609039580751</v>
+        <v>0.1216750529763788</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0914821103513479</v>
+        <v>0.1053493104666461</v>
       </c>
       <c r="F44" t="n">
-        <v>6.518019737831039</v>
+        <v>7.452956758557298</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>796.8231448710821</v>
+        <v>905.2935191342697</v>
       </c>
       <c r="I44" t="n">
-        <v>7373.833788955063</v>
+        <v>7440.255804203493</v>
       </c>
       <c r="J44" t="n">
-        <v>1.347967430149884</v>
+        <v>1.871399677575436</v>
       </c>
       <c r="K44" t="n">
-        <v>1.098145616636176</v>
+        <v>1.698951889861906</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1181322542476465</v>
+        <v>0.1207084221316547</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1021563892883647</v>
+        <v>0.1047792268804164</v>
       </c>
       <c r="F45" t="n">
-        <v>7.394419929608456</v>
+        <v>7.577810443517059</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>901.7933026164155</v>
+        <v>918.288541145271</v>
       </c>
       <c r="I45" t="n">
-        <v>7633.760215274838</v>
+        <v>7607.493536314381</v>
       </c>
       <c r="J45" t="n">
-        <v>1.567926860869972</v>
+        <v>1.86817195947087</v>
       </c>
       <c r="K45" t="n">
-        <v>1.071799870435109</v>
+        <v>1.678203627062566</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1232798328362171</v>
+        <v>0.1204954048934199</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1077351490212564</v>
+        <v>0.1049013517886933</v>
       </c>
       <c r="F46" t="n">
-        <v>7.930674840588827</v>
+        <v>7.727010039288466</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>964.881211384007</v>
+        <v>944.4849925058942</v>
       </c>
       <c r="I46" t="n">
-        <v>7826.756324904301</v>
+        <v>7838.348635296975</v>
       </c>
       <c r="J46" t="n">
-        <v>1.645847858602487</v>
+        <v>1.901881795280356</v>
       </c>
       <c r="K46" t="n">
-        <v>1.03751635647788</v>
+        <v>1.709306265265266</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1245071683981215</v>
+        <v>0.1220172072474397</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1093076400716999</v>
+        <v>0.1067744504288188</v>
       </c>
       <c r="F47" t="n">
-        <v>8.191515271015968</v>
+        <v>8.004930387551756</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1000.900847325988</v>
+        <v>977.3184738890983</v>
       </c>
       <c r="I47" t="n">
-        <v>8038.901375746723</v>
+        <v>8009.677453993732</v>
       </c>
       <c r="J47" t="n">
-        <v>1.698056131958137</v>
+        <v>1.840840942502497</v>
       </c>
       <c r="K47" t="n">
-        <v>1.024696375436378</v>
+        <v>1.703476230320227</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1279378612699769</v>
+        <v>0.12544326498</v>
       </c>
       <c r="E48" t="n">
-        <v>0.113106872516065</v>
+        <v>0.1105698511191158</v>
       </c>
       <c r="F48" t="n">
-        <v>8.626387855376858</v>
+        <v>8.434060004872432</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1041.733259007402</v>
+        <v>1028.041720660191</v>
       </c>
       <c r="I48" t="n">
-        <v>8142.493931558833</v>
+        <v>8195.272347416154</v>
       </c>
       <c r="J48" t="n">
-        <v>1.811530287591399</v>
+        <v>1.907928818326151</v>
       </c>
       <c r="K48" t="n">
-        <v>1.011367841941263</v>
+        <v>1.753688753008888</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1324739318838206</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1180151640818844</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F49" t="n">
-        <v>9.162186826603561</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1099.30803902438</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I49" t="n">
-        <v>8298.297056574651</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J49" t="n">
-        <v>1.963005611137663</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K49" t="n">
-        <v>1.000680674263687</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
   </sheetData>
